--- a/output/BookRepository.xlsx
+++ b/output/BookRepository.xlsx
@@ -12,14 +12,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="151">
+  <si>
+    <t/>
+  </si>
   <si>
     <t>Repository</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>BookRepository</t>
   </si>
   <si>
@@ -68,6 +68,9 @@
     <t>INPUT</t>
   </si>
   <si>
+    <t>書籍ID</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -200,6 +203,9 @@
     <t>書籍を保存する。</t>
   </si>
   <si>
+    <t>書籍</t>
+  </si>
+  <si>
     <t>book</t>
   </si>
   <si>
@@ -209,7 +215,7 @@
     <t>条件に一致する書籍を検索する。</t>
   </si>
   <si>
-    <t>書籍検索条件。</t>
+    <t>検索条件</t>
   </si>
   <si>
     <t>condition</t>
@@ -272,7 +278,7 @@
     <t xml:space="preserve">  onlyAvailable</t>
   </si>
   <si>
-    <t>ページング要求を表す共通DTO。</t>
+    <t>ページング要求</t>
   </si>
   <si>
     <t>pageRequest</t>
@@ -354,6 +360,9 @@
   </si>
   <si>
     <t>著者名に一致する書籍件数を取得する。</t>
+  </si>
+  <si>
+    <t>著者名</t>
   </si>
   <si>
     <t>author</t>
@@ -376,6 +385,9 @@
 将来の拡張試験用: List&amp;lt;Book&amp;gt;（現在のツールでは未対応）</t>
   </si>
   <si>
+    <t>出版日</t>
+  </si>
+  <si>
     <t>publishedDate</t>
   </si>
   <si>
@@ -386,6 +398,9 @@
 将来の拡張試験用: Book[]（現在のツールでは未対応）</t>
   </si>
   <si>
+    <t>書籍ID配列</t>
+  </si>
+  <si>
     <t>ids</t>
   </si>
   <si>
@@ -393,6 +408,66 @@
   </si>
   <si>
     <t>Book[]</t>
+  </si>
+  <si>
+    <t>XML</t>
+  </si>
+  <si>
+    <t>BookRepository.xml</t>
+  </si>
+  <si>
+    <t>&lt;?xml version="1.0" encoding="UTF-8"?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;!DOCTYPE mapper PUBLIC "-//mybatis.org//DTD Mapper 3.0//EN"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "http://mybatis.org/dtd/mybatis-3-mapper.dtd"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;mapper namespace="com.example.repository.BookRepository"&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &lt;select id="findById" resultType="com.example.entity.Book"&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        SELECT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            id,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            isbn,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            title,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        FROM book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        WHERE id = #{id}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &lt;/select&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &lt;insert id="save"&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        INSERT INTO book (isbn, title, author)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        VALUES (#{book.isbn}, #{book.title}, #{book.author})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    &lt;/insert&gt;</t>
+  </si>
+  <si>
+    <t>&lt;/mapper&gt;</t>
   </si>
 </sst>
 </file>
@@ -477,12 +552,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true">
       <alignment wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true">
+      <alignment wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true">
       <alignment wrapText="true"/>
@@ -493,12 +571,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H163"/>
+  <dimension ref="A1:H193"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.56640625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="6.94921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="44.91015625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="59.01171875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="14.296875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="17.875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="8.296875" customWidth="true" bestFit="true"/>
@@ -511,4237 +589,5017 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="H1" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H1" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D2" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H2" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s" s="2">
-        <v>1</v>
+      <c r="A4" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="H5" t="s" s="2">
-        <v>1</v>
+      <c r="A5" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s" s="1">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s" s="1">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="D6" t="s" s="1">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="F6" t="s" s="1">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="H6" t="s" s="1">
-        <v>16</v>
+      <c r="A6" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="s" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D7" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="3">
         <v>1</v>
       </c>
-      <c r="B8" t="n" s="3">
-        <v>1.0</v>
+      <c r="B8" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C8" t="s" s="3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D8" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F8" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="s" s="3">
-        <v>19</v>
-      </c>
-      <c r="H8" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H8" t="s" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="s" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D9" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="H9" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H9" t="s" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B10" t="n" s="3">
-        <v>1.0</v>
+        <v>0</v>
+      </c>
+      <c r="B10" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C10" t="s" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D10" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="s" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F10" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="s" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H10" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B11" t="n" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="C11" t="s" s="3">
-        <v>23</v>
-      </c>
-      <c r="D11" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s" s="3">
-        <v>24</v>
-      </c>
-      <c r="F11" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s" s="3">
-        <v>19</v>
-      </c>
-      <c r="H11" t="s" s="4">
-        <v>1</v>
+      <c r="A11" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B12" t="n" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="C12" t="s" s="3">
-        <v>25</v>
-      </c>
-      <c r="D12" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="F12" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="H12" t="s" s="4">
-        <v>1</v>
+      <c r="A12" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B13" t="n" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="C13" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="D13" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="F13" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="H13" t="s" s="4">
-        <v>1</v>
+      <c r="A13" t="s" s="1">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s" s="1">
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B14" t="n" s="3">
-        <v>5.0</v>
+        <v>17</v>
+      </c>
+      <c r="B14" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C14" t="s" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D14" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="s" s="3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F14" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="s" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H14" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B15" t="n" s="3">
-        <v>6.0</v>
+        <v>0</v>
+      </c>
+      <c r="B15" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C15" t="s" s="3">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="s" s="3">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="s" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H15" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B16" t="n" s="3">
-        <v>7.0</v>
+        <v>21</v>
+      </c>
+      <c r="B16" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C16" t="s" s="3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="D16" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="s" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F16" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="s" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H16" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B17" t="n" s="3">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="C17" t="s" s="3">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="s" s="3">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="s" s="3">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="H17" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B18" t="n" s="3">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="C18" t="s" s="3">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="s" s="3">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F18" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="s" s="3">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H18" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B19" t="n" s="3">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="C19" t="s" s="3">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D19" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="s" s="3">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F19" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="s" s="3">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="H19" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B20" t="n" s="3">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="C20" t="s" s="3">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D20" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="s" s="3">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F20" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="s" s="3">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H20" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B21" t="n" s="3">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="C21" t="s" s="3">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="s" s="3">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F21" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="s" s="3">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="H21" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B22" t="n" s="3">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
       <c r="C22" t="s" s="3">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="s" s="3">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F22" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="s" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H22" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B23" t="n" s="3">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="C23" t="s" s="3">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D23" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="s" s="3">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F23" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="s" s="3">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H23" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B24" t="n" s="3">
-        <v>15.0</v>
+        <v>8.0</v>
       </c>
       <c r="C24" t="s" s="3">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="s" s="3">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="F24" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="s" s="3">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H24" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B25" t="n" s="3">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
       <c r="C25" t="s" s="3">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D25" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="s" s="3">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="F25" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="s" s="3">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H25" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B26" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="B26" t="n" s="3">
+        <v>10.0</v>
       </c>
       <c r="C26" t="s" s="3">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="s" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F26" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="s" s="3">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="H26" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>5</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="D27" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="F27" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="G27" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>1</v>
+      <c r="A27" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B27" t="n" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="C27" t="s" s="3">
+        <v>47</v>
+      </c>
+      <c r="D27" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="F27" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" t="s" s="3">
+        <v>49</v>
+      </c>
+      <c r="H27" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="D28" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="E28" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="F28" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="G28" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>1</v>
+      <c r="A28" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B28" t="n" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="C28" t="s" s="3">
+        <v>50</v>
+      </c>
+      <c r="D28" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E28" t="s" s="3">
+        <v>51</v>
+      </c>
+      <c r="F28" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G28" t="s" s="3">
+        <v>52</v>
+      </c>
+      <c r="H28" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="s" s="1">
-        <v>9</v>
-      </c>
-      <c r="B29" t="s" s="1">
-        <v>10</v>
-      </c>
-      <c r="C29" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="D29" t="s" s="1">
-        <v>12</v>
-      </c>
-      <c r="E29" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="F29" t="s" s="1">
-        <v>14</v>
-      </c>
-      <c r="G29" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="H29" t="s" s="1">
-        <v>16</v>
+      <c r="A29" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B29" t="n" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="C29" t="s" s="3">
+        <v>53</v>
+      </c>
+      <c r="D29" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" t="s" s="3">
+        <v>54</v>
+      </c>
+      <c r="F29" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="H29" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="3">
-        <v>17</v>
-      </c>
-      <c r="B30" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="B30" t="n" s="3">
+        <v>14.0</v>
       </c>
       <c r="C30" t="s" s="3">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="D30" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="s" s="3">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="F30" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="s" s="3">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="H30" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B31" t="n" s="3">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="C31" t="s" s="3">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="D31" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="s" s="3">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="s" s="3">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H31" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B32" t="n" s="3">
-        <v>2.0</v>
+        <v>16.0</v>
       </c>
       <c r="C32" t="s" s="3">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="D32" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="s" s="3">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F32" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="s" s="3">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="H32" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B33" t="n" s="3">
-        <v>3.0</v>
+        <v>0</v>
+      </c>
+      <c r="B33" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C33" t="s" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D33" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="s" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F33" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="s" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H33" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B34" t="n" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="C34" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="D34" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="E34" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="F34" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="G34" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="H34" t="s" s="4">
-        <v>1</v>
+      <c r="A34" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B35" t="n" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="C35" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="D35" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="E35" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="F35" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="G35" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="H35" t="s" s="4">
-        <v>1</v>
+      <c r="A35" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B36" t="n" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="C36" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="D36" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="E36" t="s" s="3">
-        <v>33</v>
-      </c>
-      <c r="F36" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="G36" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="H36" t="s" s="4">
-        <v>1</v>
+      <c r="A36" t="s" s="1">
+        <v>9</v>
+      </c>
+      <c r="B36" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C36" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="D36" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="E36" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="F36" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="G36" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s" s="1">
+        <v>16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B37" t="n" s="3">
-        <v>7.0</v>
+        <v>17</v>
+      </c>
+      <c r="B37" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C37" t="s" s="3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="D37" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="s" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F37" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="s" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H37" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B38" t="n" s="3">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="C38" t="s" s="3">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="D38" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="s" s="3">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F38" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="s" s="3">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="H38" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B39" t="n" s="3">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="C39" t="s" s="3">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D39" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="s" s="3">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="s" s="3">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H39" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B40" t="n" s="3">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="C40" t="s" s="3">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D40" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" t="s" s="3">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F40" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" t="s" s="3">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="H40" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B41" t="n" s="3">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="C41" t="s" s="3">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D41" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="s" s="3">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F41" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="s" s="3">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H41" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B42" t="n" s="3">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="C42" t="s" s="3">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D42" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="s" s="3">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F42" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="s" s="3">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="H42" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B43" t="n" s="3">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
       <c r="C43" t="s" s="3">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="D43" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="s" s="3">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F43" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="s" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H43" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B44" t="n" s="3">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="C44" t="s" s="3">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D44" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" t="s" s="3">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F44" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="s" s="3">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H44" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B45" t="n" s="3">
-        <v>15.0</v>
+        <v>8.0</v>
       </c>
       <c r="C45" t="s" s="3">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="D45" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="s" s="3">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="F45" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="s" s="3">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H45" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B46" t="n" s="3">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
       <c r="C46" t="s" s="3">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D46" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="s" s="3">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="F46" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" t="s" s="3">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H46" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="3">
-        <v>20</v>
-      </c>
-      <c r="B47" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="B47" t="n" s="3">
+        <v>10.0</v>
       </c>
       <c r="C47" t="s" s="3">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D47" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="s" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F47" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" t="s" s="3">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="H47" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B48" t="n" s="3">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="C48" t="s" s="3">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="D48" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="s" s="3">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="F48" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="s" s="3">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="H48" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B49" t="n" s="3">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="C49" t="s" s="3">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="D49" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="s" s="3">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="F49" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" t="s" s="3">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="H49" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B50" t="n" s="3">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
       <c r="C50" t="s" s="3">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="D50" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="s" s="3">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="F50" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="s" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H50" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B51" t="n" s="3">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
       <c r="C51" t="s" s="3">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="D51" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="s" s="3">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="F51" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="s" s="3">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H51" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B52" t="n" s="3">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="C52" t="s" s="3">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="D52" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="s" s="3">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="F52" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" t="s" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H52" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B53" t="n" s="3">
-        <v>6.0</v>
+        <v>16.0</v>
       </c>
       <c r="C53" t="s" s="3">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D53" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="s" s="3">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="F53" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="s" s="3">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H53" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B54" t="n" s="3">
-        <v>7.0</v>
+        <v>21</v>
+      </c>
+      <c r="B54" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C54" t="s" s="3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="D54" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="s" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F54" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="s" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H54" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B55" t="n" s="3">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="C55" t="s" s="3">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D55" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="s" s="3">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F55" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="s" s="3">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="H55" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B56" t="n" s="3">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="C56" t="s" s="3">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D56" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="s" s="3">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F56" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" t="s" s="3">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H56" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B57" t="n" s="3">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="C57" t="s" s="3">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D57" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="s" s="3">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F57" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="s" s="3">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="H57" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B58" t="n" s="3">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="C58" t="s" s="3">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D58" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="s" s="3">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F58" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" t="s" s="3">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H58" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B59" t="n" s="3">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="C59" t="s" s="3">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D59" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" t="s" s="3">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F59" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="s" s="3">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="H59" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B60" t="n" s="3">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
       <c r="C60" t="s" s="3">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="D60" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" t="s" s="3">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F60" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" t="s" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H60" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B61" t="n" s="3">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="C61" t="s" s="3">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D61" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" t="s" s="3">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F61" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" t="s" s="3">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H61" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B62" t="n" s="3">
-        <v>15.0</v>
+        <v>8.0</v>
       </c>
       <c r="C62" t="s" s="3">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="D62" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" t="s" s="3">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="F62" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" t="s" s="3">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H62" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B63" t="n" s="3">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
       <c r="C63" t="s" s="3">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D63" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" t="s" s="3">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="F63" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="s" s="3">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H63" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B64" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="B64" t="n" s="3">
+        <v>10.0</v>
       </c>
       <c r="C64" t="s" s="3">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="D64" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="s" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F64" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" t="s" s="3">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="H64" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>5</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="D65" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="E65" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="F65" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>1</v>
+      <c r="A65" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B65" t="n" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="C65" t="s" s="3">
+        <v>47</v>
+      </c>
+      <c r="D65" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E65" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="F65" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G65" t="s" s="3">
+        <v>49</v>
+      </c>
+      <c r="H65" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="D66" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="E66" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="F66" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>1</v>
+      <c r="A66" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B66" t="n" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="C66" t="s" s="3">
+        <v>50</v>
+      </c>
+      <c r="D66" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E66" t="s" s="3">
+        <v>51</v>
+      </c>
+      <c r="F66" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G66" t="s" s="3">
+        <v>52</v>
+      </c>
+      <c r="H66" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="s" s="1">
-        <v>9</v>
-      </c>
-      <c r="B67" t="s" s="1">
-        <v>10</v>
-      </c>
-      <c r="C67" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="D67" t="s" s="1">
-        <v>12</v>
-      </c>
-      <c r="E67" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="F67" t="s" s="1">
-        <v>14</v>
-      </c>
-      <c r="G67" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="H67" t="s" s="1">
-        <v>16</v>
+      <c r="A67" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B67" t="n" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="C67" t="s" s="3">
+        <v>53</v>
+      </c>
+      <c r="D67" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E67" t="s" s="3">
+        <v>54</v>
+      </c>
+      <c r="F67" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G67" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="H67" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="3">
-        <v>17</v>
-      </c>
-      <c r="B68" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="B68" t="n" s="3">
+        <v>14.0</v>
       </c>
       <c r="C68" t="s" s="3">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="D68" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="s" s="3">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="F68" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" t="s" s="3">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="H68" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B69" t="n" s="3">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="C69" t="s" s="3">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D69" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" t="s" s="3">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F69" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" t="s" s="3">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="H69" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B70" t="n" s="3">
-        <v>2.0</v>
+        <v>16.0</v>
       </c>
       <c r="C70" t="s" s="3">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D70" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" t="s" s="3">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F70" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70" t="s" s="3">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H70" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B71" t="n" s="3">
-        <v>3.0</v>
+        <v>0</v>
+      </c>
+      <c r="B71" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C71" t="s" s="3">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D71" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="s" s="3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F71" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" t="s" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H71" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B72" t="n" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="C72" t="s" s="3">
-        <v>25</v>
-      </c>
-      <c r="D72" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="E72" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="F72" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="G72" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="H72" t="s" s="4">
-        <v>1</v>
+      <c r="A72" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="D72" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="E72" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="F72" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B73" t="n" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="C73" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="D73" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="E73" t="s" s="3">
-        <v>71</v>
-      </c>
-      <c r="F73" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="G73" t="s" s="3">
-        <v>36</v>
-      </c>
-      <c r="H73" t="s" s="4">
-        <v>1</v>
+      <c r="A73" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="D73" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="E73" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="F73" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B74" t="n" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="C74" t="s" s="3">
-        <v>72</v>
-      </c>
-      <c r="D74" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="E74" t="s" s="3">
-        <v>73</v>
-      </c>
-      <c r="F74" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="G74" t="s" s="3">
-        <v>36</v>
-      </c>
-      <c r="H74" t="s" s="4">
-        <v>1</v>
+      <c r="A74" t="s" s="1">
+        <v>9</v>
+      </c>
+      <c r="B74" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C74" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="D74" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="E74" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="F74" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="G74" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H74" t="s" s="1">
+        <v>16</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B75" t="n" s="3">
-        <v>7.0</v>
+        <v>17</v>
+      </c>
+      <c r="B75" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C75" t="s" s="3">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D75" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" t="s" s="3">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F75" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="s" s="3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="H75" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B76" t="n" s="3">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="C76" t="s" s="3">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D76" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" t="s" s="3">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F76" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" t="s" s="3">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="H76" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B77" t="n" s="3">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="C77" t="s" s="3">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D77" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77" t="s" s="3">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="F77" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" t="s" s="3">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H77" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B78" t="n" s="3">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="C78" t="s" s="3">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D78" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" t="s" s="3">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="F78" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="s" s="3">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H78" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B79" t="n" s="3">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="C79" t="s" s="3">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="D79" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" t="s" s="3">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="F79" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" t="s" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H79" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B80" t="n" s="3">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="C80" t="s" s="3">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D80" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" t="s" s="3">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="F80" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="s" s="3">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H80" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B81" t="n" s="3">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
       <c r="C81" t="s" s="3">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D81" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" t="s" s="3">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="F81" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" t="s" s="3">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="H81" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B82" t="n" s="3">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="C82" t="s" s="3">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D82" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82" t="s" s="3">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F82" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" t="s" s="3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H82" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B83" t="n" s="3">
-        <v>15.0</v>
+        <v>8.0</v>
       </c>
       <c r="C83" t="s" s="3">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D83" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="s" s="3">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F83" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" t="s" s="3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H83" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B84" t="n" s="3">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
       <c r="C84" t="s" s="3">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D84" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84" t="s" s="3">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F84" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" t="s" s="3">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="H84" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B85" t="n" s="3">
-        <v>17.0</v>
+        <v>10.0</v>
       </c>
       <c r="C85" t="s" s="3">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D85" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" t="s" s="3">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F85" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" t="s" s="3">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="H85" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="3">
-        <v>20</v>
-      </c>
-      <c r="B86" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="B86" t="n" s="3">
+        <v>11.0</v>
       </c>
       <c r="C86" t="s" s="3">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="D86" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" t="s" s="3">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="F86" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" t="s" s="3">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="H86" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B87" t="n" s="3">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="C87" t="s" s="3">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D87" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" t="s" s="3">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F87" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="s" s="3">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="H87" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B88" t="n" s="3">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="C88" t="s" s="3">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D88" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" t="s" s="3">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F88" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="s" s="3">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H88" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B89" t="n" s="3">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="C89" t="s" s="3">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D89" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" t="s" s="3">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="F89" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" t="s" s="3">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="H89" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B90" t="n" s="3">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="C90" t="s" s="3">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D90" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" t="s" s="3">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="F90" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" t="s" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H90" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B91" t="n" s="3">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
       <c r="C91" t="s" s="3">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="D91" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="s" s="3">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="F91" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91" t="s" s="3">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="H91" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B92" t="n" s="3">
-        <v>6.0</v>
+        <v>17.0</v>
       </c>
       <c r="C92" t="s" s="3">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D92" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92" t="s" s="3">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F92" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" t="s" s="3">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H92" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B93" t="n" s="3">
-        <v>7.0</v>
+        <v>21</v>
+      </c>
+      <c r="B93" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C93" t="s" s="3">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D93" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" t="s" s="3">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="F93" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" t="s" s="3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H93" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B94" t="n" s="3">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="C94" t="s" s="3">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D94" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" t="s" s="3">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="F94" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="s" s="3">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="H94" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B95" t="n" s="3">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="C95" t="s" s="3">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D95" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" t="s" s="3">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="F95" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" t="s" s="3">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="H95" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B96" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="B96" t="n" s="3">
+        <v>3.0</v>
       </c>
       <c r="C96" t="s" s="3">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="D96" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="s" s="3">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="F96" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="s" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H96" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="s" s="2">
-        <v>5</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="D97" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="E97" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="F97" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>1</v>
+      <c r="A97" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B97" t="n" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="C97" t="s" s="3">
+        <v>100</v>
+      </c>
+      <c r="D97" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E97" t="s" s="3">
+        <v>101</v>
+      </c>
+      <c r="F97" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G97" t="s" s="3">
+        <v>43</v>
+      </c>
+      <c r="H97" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C98" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="D98" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="E98" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="F98" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>1</v>
+      <c r="A98" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B98" t="n" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="C98" t="s" s="3">
+        <v>102</v>
+      </c>
+      <c r="D98" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E98" t="s" s="3">
+        <v>103</v>
+      </c>
+      <c r="F98" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G98" t="s" s="3">
+        <v>90</v>
+      </c>
+      <c r="H98" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="s" s="1">
-        <v>9</v>
-      </c>
-      <c r="B99" t="s" s="1">
-        <v>10</v>
-      </c>
-      <c r="C99" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="D99" t="s" s="1">
-        <v>12</v>
-      </c>
-      <c r="E99" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="F99" t="s" s="1">
-        <v>14</v>
-      </c>
-      <c r="G99" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="H99" t="s" s="1">
-        <v>16</v>
+      <c r="A99" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B99" t="n" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="C99" t="s" s="3">
+        <v>104</v>
+      </c>
+      <c r="D99" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E99" t="s" s="3">
+        <v>105</v>
+      </c>
+      <c r="F99" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G99" t="s" s="3">
+        <v>43</v>
+      </c>
+      <c r="H99" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="3">
-        <v>17</v>
-      </c>
-      <c r="B100" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="B100" t="n" s="3">
+        <v>7.0</v>
       </c>
       <c r="C100" t="s" s="3">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="D100" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" t="s" s="3">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="F100" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" t="s" s="3">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="H100" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B101" t="n" s="3">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="C101" t="s" s="3">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="D101" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" t="s" s="3">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="F101" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" t="s" s="3">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H101" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B102" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="B102" t="n" s="3">
+        <v>9.0</v>
       </c>
       <c r="C102" t="s" s="3">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="D102" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102" t="s" s="3">
-        <v>1</v>
+        <v>111</v>
       </c>
       <c r="F102" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" t="s" s="3">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="H102" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="s" s="2">
-        <v>5</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="D103" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="E103" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="F103" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>1</v>
+      <c r="A103" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B103" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C103" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="D103" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E103" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F103" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G103" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H103" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="D104" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="E104" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="F104" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
         <v>7</v>
       </c>
-      <c r="B104" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C104" t="s" s="2">
+      <c r="B105" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="C105" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="D104" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="E104" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="F104" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s" s="1">
+      <c r="D105" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="E105" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="F105" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="1">
         <v>9</v>
       </c>
-      <c r="B105" t="s" s="1">
+      <c r="B106" t="s" s="1">
         <v>10</v>
       </c>
-      <c r="C105" t="s" s="1">
+      <c r="C106" t="s" s="1">
         <v>11</v>
       </c>
-      <c r="D105" t="s" s="1">
+      <c r="D106" t="s" s="1">
         <v>12</v>
       </c>
-      <c r="E105" t="s" s="1">
+      <c r="E106" t="s" s="1">
         <v>13</v>
       </c>
-      <c r="F105" t="s" s="1">
+      <c r="F106" t="s" s="1">
         <v>14</v>
       </c>
-      <c r="G105" t="s" s="1">
+      <c r="G106" t="s" s="1">
         <v>15</v>
       </c>
-      <c r="H105" t="s" s="1">
+      <c r="H106" t="s" s="1">
         <v>16</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s" s="3">
-        <v>17</v>
-      </c>
-      <c r="B106" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="C106" t="s" s="3">
-        <v>17</v>
-      </c>
-      <c r="D106" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="E106" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="F106" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="G106" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="H106" t="s" s="4">
-        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B107" t="n" s="3">
-        <v>1.0</v>
+        <v>17</v>
+      </c>
+      <c r="B107" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C107" t="s" s="3">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="D107" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E107" t="s" s="3">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="F107" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107" t="s" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H107" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B108" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C108" t="s" s="3">
+        <v>18</v>
+      </c>
+      <c r="D108" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E108" t="s" s="3">
+        <v>19</v>
+      </c>
+      <c r="F108" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G108" t="s" s="3">
         <v>20</v>
       </c>
-      <c r="B108" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="C108" t="s" s="3">
-        <v>20</v>
-      </c>
-      <c r="D108" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="E108" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="F108" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="G108" t="s" s="3">
-        <v>1</v>
-      </c>
       <c r="H108" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B109" t="n" s="3">
-        <v>1.0</v>
+        <v>0</v>
+      </c>
+      <c r="B109" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C109" t="s" s="3">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="D109" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E109" t="s" s="3">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="F109" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G109" t="s" s="3">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="H109" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B110" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="C110" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="D110" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="E110" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="F110" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="G110" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="H110" t="s" s="4">
-        <v>1</v>
+      <c r="A110" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="D110" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="E110" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="F110" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D111" t="s" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E111" t="s" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" t="s" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="D112" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="E112" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="F112" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>1</v>
+      <c r="A112" t="s" s="1">
+        <v>9</v>
+      </c>
+      <c r="B112" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C112" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="D112" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="E112" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="F112" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="G112" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H112" t="s" s="1">
+        <v>16</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="s" s="1">
-        <v>9</v>
-      </c>
-      <c r="B113" t="s" s="1">
-        <v>10</v>
-      </c>
-      <c r="C113" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="D113" t="s" s="1">
-        <v>12</v>
-      </c>
-      <c r="E113" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="F113" t="s" s="1">
-        <v>14</v>
-      </c>
-      <c r="G113" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="H113" t="s" s="1">
-        <v>16</v>
+      <c r="A113" t="s" s="3">
+        <v>17</v>
+      </c>
+      <c r="B113" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C113" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="D113" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E113" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F113" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G113" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H113" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B114" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C114" t="s" s="3">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="D114" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" t="s" s="3">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="F114" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G114" t="s" s="3">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="H114" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B115" t="n" s="3">
-        <v>1.0</v>
+        <v>21</v>
+      </c>
+      <c r="B115" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C115" t="s" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D115" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E115" t="s" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F115" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G115" t="s" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H115" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B116" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C116" t="s" s="3">
-        <v>20</v>
+        <v>118</v>
       </c>
       <c r="D116" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E116" t="s" s="3">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="F116" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116" t="s" s="3">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="H116" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B117" t="n" s="3">
-        <v>1.0</v>
+        <v>0</v>
+      </c>
+      <c r="B117" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C117" t="s" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D117" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E117" t="s" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F117" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117" t="s" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H117" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B118" t="n" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="C118" t="s" s="3">
-        <v>23</v>
-      </c>
-      <c r="D118" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="E118" t="s" s="3">
-        <v>24</v>
-      </c>
-      <c r="F118" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="G118" t="s" s="3">
-        <v>19</v>
-      </c>
-      <c r="H118" t="s" s="4">
-        <v>1</v>
+      <c r="A118" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="D118" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="E118" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="F118" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B119" t="n" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="C119" t="s" s="3">
-        <v>25</v>
-      </c>
-      <c r="D119" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="E119" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="F119" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="G119" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="H119" t="s" s="4">
-        <v>1</v>
+      <c r="A119" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="D119" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="E119" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="F119" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B120" t="n" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="C120" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="D120" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="E120" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="F120" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="G120" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="H120" t="s" s="4">
-        <v>1</v>
+      <c r="A120" t="s" s="1">
+        <v>9</v>
+      </c>
+      <c r="B120" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C120" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="D120" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="E120" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="F120" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="G120" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H120" t="s" s="1">
+        <v>16</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B121" t="n" s="3">
-        <v>5.0</v>
+        <v>17</v>
+      </c>
+      <c r="B121" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C121" t="s" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D121" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" t="s" s="3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F121" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" t="s" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H121" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B122" t="n" s="3">
-        <v>6.0</v>
+        <v>0</v>
+      </c>
+      <c r="B122" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C122" t="s" s="3">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D122" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E122" t="s" s="3">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F122" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" t="s" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H122" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B123" t="n" s="3">
-        <v>7.0</v>
+        <v>21</v>
+      </c>
+      <c r="B123" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C123" t="s" s="3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="D123" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123" t="s" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F123" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G123" t="s" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H123" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B124" t="n" s="3">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="C124" t="s" s="3">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D124" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124" t="s" s="3">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F124" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124" t="s" s="3">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="H124" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B125" t="n" s="3">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="C125" t="s" s="3">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D125" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E125" t="s" s="3">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F125" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125" t="s" s="3">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H125" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B126" t="n" s="3">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="C126" t="s" s="3">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D126" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126" t="s" s="3">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F126" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126" t="s" s="3">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="H126" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B127" t="n" s="3">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="C127" t="s" s="3">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D127" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E127" t="s" s="3">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F127" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G127" t="s" s="3">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H127" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B128" t="n" s="3">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="C128" t="s" s="3">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D128" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128" t="s" s="3">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F128" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128" t="s" s="3">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="H128" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B129" t="n" s="3">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
       <c r="C129" t="s" s="3">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="D129" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129" t="s" s="3">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F129" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G129" t="s" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H129" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B130" t="n" s="3">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="C130" t="s" s="3">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D130" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130" t="s" s="3">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F130" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G130" t="s" s="3">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H130" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B131" t="n" s="3">
-        <v>15.0</v>
+        <v>8.0</v>
       </c>
       <c r="C131" t="s" s="3">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="D131" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131" t="s" s="3">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="F131" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G131" t="s" s="3">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H131" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B132" t="n" s="3">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
       <c r="C132" t="s" s="3">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D132" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E132" t="s" s="3">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="F132" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G132" t="s" s="3">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H132" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B133" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="B133" t="n" s="3">
+        <v>10.0</v>
       </c>
       <c r="C133" t="s" s="3">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="D133" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E133" t="s" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F133" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G133" t="s" s="3">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="H133" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="s" s="2">
-        <v>5</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C134" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="D134" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="E134" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="F134" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="G134" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>1</v>
+      <c r="A134" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B134" t="n" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="C134" t="s" s="3">
+        <v>47</v>
+      </c>
+      <c r="D134" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E134" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="F134" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G134" t="s" s="3">
+        <v>49</v>
+      </c>
+      <c r="H134" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C135" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="D135" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="E135" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="F135" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="G135" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>1</v>
+      <c r="A135" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B135" t="n" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="C135" t="s" s="3">
+        <v>50</v>
+      </c>
+      <c r="D135" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E135" t="s" s="3">
+        <v>51</v>
+      </c>
+      <c r="F135" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G135" t="s" s="3">
+        <v>52</v>
+      </c>
+      <c r="H135" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="s" s="1">
-        <v>9</v>
-      </c>
-      <c r="B136" t="s" s="1">
-        <v>10</v>
-      </c>
-      <c r="C136" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="D136" t="s" s="1">
-        <v>12</v>
-      </c>
-      <c r="E136" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="F136" t="s" s="1">
-        <v>14</v>
-      </c>
-      <c r="G136" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="H136" t="s" s="1">
-        <v>16</v>
+      <c r="A136" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B136" t="n" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="C136" t="s" s="3">
+        <v>53</v>
+      </c>
+      <c r="D136" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E136" t="s" s="3">
+        <v>54</v>
+      </c>
+      <c r="F136" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G136" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="H136" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="3">
-        <v>17</v>
-      </c>
-      <c r="B137" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="B137" t="n" s="3">
+        <v>14.0</v>
       </c>
       <c r="C137" t="s" s="3">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="D137" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E137" t="s" s="3">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="F137" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" t="s" s="3">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="H137" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B138" t="n" s="3">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="C138" t="s" s="3">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="D138" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E138" t="s" s="3">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="F138" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G138" t="s" s="3">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H138" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="3">
-        <v>20</v>
-      </c>
-      <c r="B139" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="B139" t="n" s="3">
+        <v>16.0</v>
       </c>
       <c r="C139" t="s" s="3">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="D139" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E139" t="s" s="3">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="F139" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G139" t="s" s="3">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="H139" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B140" t="n" s="3">
-        <v>1.0</v>
+        <v>0</v>
+      </c>
+      <c r="B140" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C140" t="s" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D140" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E140" t="s" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F140" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G140" t="s" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H140" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B141" t="n" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="C141" t="s" s="3">
-        <v>23</v>
-      </c>
-      <c r="D141" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="E141" t="s" s="3">
-        <v>24</v>
-      </c>
-      <c r="F141" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="G141" t="s" s="3">
-        <v>19</v>
-      </c>
-      <c r="H141" t="s" s="4">
-        <v>1</v>
+      <c r="A141" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="C141" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="D141" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="E141" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="F141" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B142" t="n" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="C142" t="s" s="3">
-        <v>25</v>
-      </c>
-      <c r="D142" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="E142" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="F142" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="G142" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="H142" t="s" s="4">
-        <v>1</v>
+      <c r="A142" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="C142" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="D142" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="E142" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="F142" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B143" t="n" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="C143" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="D143" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="E143" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="F143" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="G143" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="H143" t="s" s="4">
-        <v>1</v>
+      <c r="A143" t="s" s="1">
+        <v>9</v>
+      </c>
+      <c r="B143" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C143" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="D143" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="E143" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="F143" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="G143" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H143" t="s" s="1">
+        <v>16</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B144" t="n" s="3">
-        <v>5.0</v>
+        <v>17</v>
+      </c>
+      <c r="B144" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C144" t="s" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D144" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E144" t="s" s="3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F144" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G144" t="s" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H144" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B145" t="n" s="3">
-        <v>6.0</v>
+        <v>0</v>
+      </c>
+      <c r="B145" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C145" t="s" s="3">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="D145" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E145" t="s" s="3">
-        <v>33</v>
+        <v>124</v>
       </c>
       <c r="F145" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145" t="s" s="3">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H145" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B146" t="n" s="3">
-        <v>7.0</v>
+        <v>21</v>
+      </c>
+      <c r="B146" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C146" t="s" s="3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="D146" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E146" t="s" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F146" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G146" t="s" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H146" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B147" t="n" s="3">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="C147" t="s" s="3">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D147" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E147" t="s" s="3">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F147" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G147" t="s" s="3">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="H147" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B148" t="n" s="3">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="C148" t="s" s="3">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D148" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" t="s" s="3">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F148" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G148" t="s" s="3">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H148" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B149" t="n" s="3">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="C149" t="s" s="3">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D149" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149" t="s" s="3">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F149" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G149" t="s" s="3">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="H149" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B150" t="n" s="3">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="C150" t="s" s="3">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D150" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150" t="s" s="3">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F150" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G150" t="s" s="3">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H150" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B151" t="n" s="3">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="C151" t="s" s="3">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D151" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" t="s" s="3">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F151" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G151" t="s" s="3">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="H151" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B152" t="n" s="3">
-        <v>13.0</v>
+        <v>6.0</v>
       </c>
       <c r="C152" t="s" s="3">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="D152" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E152" t="s" s="3">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F152" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G152" t="s" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H152" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B153" t="n" s="3">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="C153" t="s" s="3">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D153" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E153" t="s" s="3">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F153" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G153" t="s" s="3">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H153" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B154" t="n" s="3">
-        <v>15.0</v>
+        <v>8.0</v>
       </c>
       <c r="C154" t="s" s="3">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="D154" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E154" t="s" s="3">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="F154" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G154" t="s" s="3">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H154" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B155" t="n" s="3">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
       <c r="C155" t="s" s="3">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D155" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E155" t="s" s="3">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="F155" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G155" t="s" s="3">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H155" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B156" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="B156" t="n" s="3">
+        <v>10.0</v>
       </c>
       <c r="C156" t="s" s="3">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="D156" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156" t="s" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F156" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G156" t="s" s="3">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="H156" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="s" s="2">
-        <v>5</v>
-      </c>
-      <c r="B157" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C157" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="D157" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="E157" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="F157" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="G157" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="H157" t="s" s="2">
-        <v>1</v>
+      <c r="A157" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B157" t="n" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="C157" t="s" s="3">
+        <v>47</v>
+      </c>
+      <c r="D157" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E157" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="F157" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G157" t="s" s="3">
+        <v>49</v>
+      </c>
+      <c r="H157" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C158" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="D158" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="E158" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="F158" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="G158" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="H158" t="s" s="2">
-        <v>1</v>
+      <c r="A158" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B158" t="n" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="C158" t="s" s="3">
+        <v>50</v>
+      </c>
+      <c r="D158" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E158" t="s" s="3">
+        <v>51</v>
+      </c>
+      <c r="F158" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G158" t="s" s="3">
+        <v>52</v>
+      </c>
+      <c r="H158" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="s" s="1">
-        <v>9</v>
-      </c>
-      <c r="B159" t="s" s="1">
-        <v>10</v>
-      </c>
-      <c r="C159" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="D159" t="s" s="1">
-        <v>12</v>
-      </c>
-      <c r="E159" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="F159" t="s" s="1">
-        <v>14</v>
-      </c>
-      <c r="G159" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="H159" t="s" s="1">
-        <v>16</v>
+      <c r="A159" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B159" t="n" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="C159" t="s" s="3">
+        <v>53</v>
+      </c>
+      <c r="D159" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E159" t="s" s="3">
+        <v>54</v>
+      </c>
+      <c r="F159" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G159" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="H159" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="3">
-        <v>17</v>
-      </c>
-      <c r="B160" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="B160" t="n" s="3">
+        <v>14.0</v>
       </c>
       <c r="C160" t="s" s="3">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="D160" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E160" t="s" s="3">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="F160" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G160" t="s" s="3">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="H160" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B161" t="n" s="3">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="C161" t="s" s="3">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="D161" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E161" t="s" s="3">
-        <v>123</v>
+        <v>58</v>
       </c>
       <c r="F161" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G161" t="s" s="3">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="H161" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="3">
-        <v>20</v>
-      </c>
-      <c r="B162" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="B162" t="n" s="3">
+        <v>16.0</v>
       </c>
       <c r="C162" t="s" s="3">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="D162" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E162" t="s" s="3">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="F162" t="s" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G162" t="s" s="3">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="H162" t="s" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="B163" t="n" s="3">
-        <v>1.0</v>
+        <v>0</v>
+      </c>
+      <c r="B163" t="s" s="3">
+        <v>0</v>
       </c>
       <c r="C163" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="D163" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E163" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F163" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G163" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H163" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="C164" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="D163" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="E163" t="s" s="3">
-        <v>125</v>
-      </c>
-      <c r="F163" t="s" s="3">
-        <v>1</v>
-      </c>
-      <c r="G163" t="s" s="3">
-        <v>125</v>
-      </c>
-      <c r="H163" t="s" s="4">
-        <v>1</v>
+      <c r="D164" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="E164" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="F164" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="G164" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="H164" t="s" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="C165" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="D165" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="E165" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="F165" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="G165" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="H165" t="s" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="1">
+        <v>9</v>
+      </c>
+      <c r="B166" t="s" s="1">
+        <v>10</v>
+      </c>
+      <c r="C166" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="D166" t="s" s="1">
+        <v>12</v>
+      </c>
+      <c r="E166" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="F166" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="G166" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H166" t="s" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="3">
+        <v>17</v>
+      </c>
+      <c r="B167" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C167" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="D167" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E167" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F167" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G167" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H167" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B168" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C168" t="s" s="3">
+        <v>127</v>
+      </c>
+      <c r="D168" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E168" t="s" s="3">
+        <v>128</v>
+      </c>
+      <c r="F168" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G168" t="s" s="3">
+        <v>129</v>
+      </c>
+      <c r="H168" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="3">
+        <v>21</v>
+      </c>
+      <c r="B169" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C169" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="D169" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E169" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F169" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G169" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H169" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B170" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C170" t="s" s="3">
+        <v>130</v>
+      </c>
+      <c r="D170" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E170" t="s" s="3">
+        <v>130</v>
+      </c>
+      <c r="F170" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G170" t="s" s="3">
+        <v>130</v>
+      </c>
+      <c r="H170" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B171" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C171" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="D171" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E171" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F171" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G171" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H171" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="3">
+        <v>131</v>
+      </c>
+      <c r="B172" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C172" t="s" s="3">
+        <v>132</v>
+      </c>
+      <c r="D172" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E172" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F172" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G172" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H172" t="s" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B173" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C173" t="s" s="3">
+        <v>133</v>
+      </c>
+      <c r="D173" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E173" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F173" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G173" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H173" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B174" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C174" t="s" s="3">
+        <v>134</v>
+      </c>
+      <c r="D174" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E174" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F174" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G174" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H174" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B175" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C175" t="s" s="3">
+        <v>135</v>
+      </c>
+      <c r="D175" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E175" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F175" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G175" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H175" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B176" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C176" t="s" s="3">
+        <v>136</v>
+      </c>
+      <c r="D176" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E176" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F176" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G176" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H176" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B177" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C177" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="D177" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E177" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F177" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G177" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H177" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B178" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C178" t="s" s="3">
+        <v>137</v>
+      </c>
+      <c r="D178" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E178" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F178" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G178" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H178" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B179" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C179" t="s" s="3">
+        <v>138</v>
+      </c>
+      <c r="D179" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E179" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F179" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G179" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H179" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B180" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C180" t="s" s="3">
+        <v>139</v>
+      </c>
+      <c r="D180" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E180" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F180" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G180" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H180" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B181" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C181" t="s" s="3">
+        <v>140</v>
+      </c>
+      <c r="D181" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E181" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F181" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G181" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H181" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B182" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C182" t="s" s="3">
+        <v>141</v>
+      </c>
+      <c r="D182" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E182" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F182" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G182" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H182" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B183" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C183" t="s" s="3">
+        <v>142</v>
+      </c>
+      <c r="D183" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E183" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F183" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G183" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H183" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B184" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C184" t="s" s="3">
+        <v>143</v>
+      </c>
+      <c r="D184" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E184" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F184" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G184" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H184" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B185" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C185" t="s" s="3">
+        <v>144</v>
+      </c>
+      <c r="D185" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E185" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F185" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G185" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H185" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B186" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C186" t="s" s="3">
+        <v>145</v>
+      </c>
+      <c r="D186" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E186" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F186" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G186" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H186" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B187" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C187" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="D187" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E187" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F187" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G187" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H187" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B188" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C188" t="s" s="3">
+        <v>146</v>
+      </c>
+      <c r="D188" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E188" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F188" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G188" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H188" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B189" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C189" t="s" s="3">
+        <v>147</v>
+      </c>
+      <c r="D189" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E189" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F189" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G189" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H189" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B190" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C190" t="s" s="3">
+        <v>148</v>
+      </c>
+      <c r="D190" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E190" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F190" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G190" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H190" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B191" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C191" t="s" s="3">
+        <v>149</v>
+      </c>
+      <c r="D191" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E191" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F191" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G191" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H191" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B192" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C192" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="D192" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E192" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F192" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G192" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H192" t="s" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="B193" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="C193" t="s" s="3">
+        <v>150</v>
+      </c>
+      <c r="D193" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="E193" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="F193" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="G193" t="s" s="3">
+        <v>0</v>
+      </c>
+      <c r="H193" t="s" s="4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/BookRepository.xlsx
+++ b/output/BookRepository.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="151">
   <si>
     <t>Repository</t>
   </si>
@@ -573,7 +573,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
@@ -741,30 +741,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true">
       <alignment wrapText="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
-      <alignment wrapText="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
-      <alignment wrapText="false"/>
-    </xf>
   </cellXfs>
 </styleSheet>
 </file>
@@ -4810,550 +4786,109 @@
       <c r="G172" s="73"/>
       <c r="H172" s="74"/>
     </row>
-    <row r="173" ht="15.0" customHeight="true">
+    <row r="173">
       <c r="A173" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B173" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C173" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D173" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E173" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G173" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H173" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="174" ht="15.0" customHeight="true">
+    </row>
+    <row r="174">
       <c r="A174" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B174" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C174" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D174" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E174" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G174" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H174" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="175" ht="15.0" customHeight="true">
+    </row>
+    <row r="175">
       <c r="A175" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C175" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D175" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E175" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F175" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G175" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H175" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="176" ht="15.0" customHeight="true">
+    </row>
+    <row r="176">
       <c r="A176" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B176" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C176" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="D176" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E176" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G176" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H176" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="177" ht="15.0" customHeight="true">
+    </row>
+    <row r="177">
       <c r="A177" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B177" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C177" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D177" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E177" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F177" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G177" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H177" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="178" ht="15.0" customHeight="true">
+    </row>
+    <row r="178">
       <c r="A178" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C178" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D178" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F178" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G178" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H178" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="179" ht="15.0" customHeight="true">
+    </row>
+    <row r="179">
       <c r="A179" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B179" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C179" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D179" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E179" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F179" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G179" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H179" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="180" ht="15.0" customHeight="true">
+    </row>
+    <row r="180">
       <c r="A180" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C180" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="D180" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E180" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F180" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G180" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H180" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="181" ht="15.0" customHeight="true">
+    </row>
+    <row r="181">
       <c r="A181" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B181" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C181" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="D181" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E181" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F181" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G181" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H181" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="182" ht="15.0" customHeight="true">
+    </row>
+    <row r="182">
       <c r="A182" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B182" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C182" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D182" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E182" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G182" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H182" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="183" ht="15.0" customHeight="true">
+    </row>
+    <row r="183">
       <c r="A183" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B183" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C183" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D183" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E183" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F183" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G183" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H183" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="184" ht="15.0" customHeight="true">
+    </row>
+    <row r="184">
       <c r="A184" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B184" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C184" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D184" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E184" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F184" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G184" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H184" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="185" ht="15.0" customHeight="true">
+    </row>
+    <row r="185">
       <c r="A185" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B185" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C185" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D185" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E185" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F185" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G185" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H185" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="186" ht="15.0" customHeight="true">
+    </row>
+    <row r="186">
       <c r="A186" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B186" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C186" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D186" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E186" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F186" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G186" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H186" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="187" ht="15.0" customHeight="true">
+    </row>
+    <row r="187">
       <c r="A187" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B187" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C187" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D187" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E187" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F187" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G187" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H187" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="188" ht="15.0" customHeight="true">
+    </row>
+    <row r="188">
       <c r="A188" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B188" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C188" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="D188" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E188" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F188" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G188" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H188" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="189" ht="15.0" customHeight="true">
+    </row>
+    <row r="189">
       <c r="A189" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B189" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C189" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D189" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E189" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F189" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G189" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H189" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="190" ht="15.0" customHeight="true">
+    </row>
+    <row r="190">
       <c r="A190" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B190" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C190" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="D190" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E190" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F190" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G190" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H190" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="191" ht="15.0" customHeight="true">
+    </row>
+    <row r="191">
       <c r="A191" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B191" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C191" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D191" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E191" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F191" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G191" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H191" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="192" ht="15.0" customHeight="true">
+    </row>
+    <row r="192">
       <c r="A192" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B192" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C192" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D192" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E192" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F192" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G192" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H192" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="193" ht="15.0" customHeight="true">
+    </row>
+    <row r="193">
       <c r="A193" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B193" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C193" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="D193" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E193" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F193" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G193" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H193" s="5" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/output/BookRepository.xlsx
+++ b/output/BookRepository.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="153">
   <si>
     <t>Repository</t>
   </si>
@@ -20,10 +20,16 @@
     <t>Repository概要</t>
   </si>
   <si>
-    <t>Method</t>
-  </si>
-  <si>
-    <t>Method概要</t>
+    <t>SQL_ID</t>
+  </si>
+  <si>
+    <t>SQL概要</t>
+  </si>
+  <si>
+    <t>selectXX</t>
+  </si>
+  <si>
+    <t>XXを取得する</t>
   </si>
   <si>
     <t>区分</t>
@@ -50,6 +56,12 @@
     <t>備考</t>
   </si>
   <si>
+    <t>●INPUT</t>
+  </si>
+  <si>
+    <t>●OUTPUT</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -65,9 +77,6 @@
     <t>IDで書籍を取得する。</t>
   </si>
   <si>
-    <t>INPUT</t>
-  </si>
-  <si>
     <t>書籍ID</t>
   </si>
   <si>
@@ -75,9 +84,6 @@
   </si>
   <si>
     <t>Long</t>
-  </si>
-  <si>
-    <t>OUTPUT</t>
   </si>
   <si>
     <t>書籍エンティティ。</t>
@@ -835,10 +841,10 @@
         <v>0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -851,10 +857,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -873,14 +879,12 @@
       <c r="H10" s="3"/>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="2">
+      <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -889,14 +893,12 @@
       <c r="H11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>3</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="A12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -906,522 +908,522 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B13" t="s" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13" t="s" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" t="s" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G13" t="s" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H13" t="s" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B15" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>16</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>21</v>
+      <c r="A16" t="s" s="3">
+        <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>12</v>
+      <c r="A17" t="s" s="3">
+        <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>1.0</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="true">
       <c r="A18" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B18" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="true">
       <c r="A19" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B19" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="true">
       <c r="A20" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B20" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E20" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>28</v>
-      </c>
       <c r="H20" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="true">
       <c r="A21" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B21" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="true">
       <c r="A22" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B22" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="true">
       <c r="A23" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B23" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" ht="15.0" customHeight="true">
       <c r="A24" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B24" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="true">
       <c r="A25" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B25" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" ht="15.0" customHeight="true">
       <c r="A26" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>10.0</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" ht="15.0" customHeight="true">
       <c r="A27" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>11.0</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="true">
       <c r="A28" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B28" s="12" t="n">
         <v>12.0</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" ht="15.0" customHeight="true">
       <c r="A29" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B29" s="12" t="n">
         <v>13.0</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" ht="15.0" customHeight="true">
       <c r="A30" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B30" s="12" t="n">
         <v>14.0</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="true">
       <c r="A31" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B31" s="12" t="n">
         <v>15.0</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" ht="15.0" customHeight="true">
       <c r="A32" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B32" s="12" t="n">
         <v>16.0</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" ht="15.0" customHeight="true">
@@ -1438,11 +1440,9 @@
       <c r="A34" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B34" s="28"/>
       <c r="C34" s="29" t="s">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="D34" s="30"/>
       <c r="E34" s="31"/>
@@ -1452,13 +1452,11 @@
     </row>
     <row r="35" ht="15.0" customHeight="true">
       <c r="A35" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="B35" s="36"/>
       <c r="C35" s="37" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D35" s="38"/>
       <c r="E35" s="39"/>
@@ -1468,912 +1466,912 @@
     </row>
     <row r="36" ht="15.0" customHeight="true">
       <c r="A36" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B36" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C36" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D36" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F36" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G36" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H36" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" ht="15.0" customHeight="true">
       <c r="A37" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B37" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C37" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D37" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E37" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F37" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G37" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H37" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" ht="15.0" customHeight="true">
       <c r="A38" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B38" s="12" t="n">
         <v>1.0</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="true">
       <c r="A39" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B39" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" ht="15.0" customHeight="true">
       <c r="A40" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B40" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" ht="15.0" customHeight="true">
       <c r="A41" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B41" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E41" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="F41" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G41" s="17" t="s">
-        <v>28</v>
-      </c>
       <c r="H41" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="true">
       <c r="A42" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B42" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" ht="15.0" customHeight="true">
       <c r="A43" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B43" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H43" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" ht="15.0" customHeight="true">
       <c r="A44" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B44" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H44" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="true">
       <c r="A45" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B45" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H45" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" ht="15.0" customHeight="true">
       <c r="A46" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B46" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H46" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" ht="15.0" customHeight="true">
       <c r="A47" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B47" s="12" t="n">
         <v>10.0</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H47" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" ht="15.0" customHeight="true">
       <c r="A48" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B48" s="12" t="n">
         <v>11.0</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H48" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" ht="15.0" customHeight="true">
       <c r="A49" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B49" s="12" t="n">
         <v>12.0</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H49" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" ht="15.0" customHeight="true">
       <c r="A50" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B50" s="12" t="n">
         <v>13.0</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H50" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="true">
       <c r="A51" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B51" s="12" t="n">
         <v>14.0</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H51" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" ht="15.0" customHeight="true">
       <c r="A52" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B52" s="12" t="n">
         <v>15.0</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H52" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" ht="15.0" customHeight="true">
       <c r="A53" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B53" s="12" t="n">
         <v>16.0</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F53" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G53" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H53" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="true">
       <c r="A54" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B54" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C54" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D54" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E54" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F54" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G54" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H54" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55" ht="15.0" customHeight="true">
       <c r="A55" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B55" s="12" t="n">
         <v>1.0</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F55" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G55" s="17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H55" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" ht="15.0" customHeight="true">
       <c r="A56" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B56" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F56" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G56" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H56" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="true">
       <c r="A57" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B57" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F57" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G57" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H57" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" ht="15.0" customHeight="true">
       <c r="A58" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B58" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E58" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F58" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="F58" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G58" s="17" t="s">
-        <v>28</v>
-      </c>
       <c r="H58" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" ht="15.0" customHeight="true">
       <c r="A59" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B59" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F59" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G59" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" ht="15.0" customHeight="true">
       <c r="A60" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B60" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G60" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H60" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" ht="15.0" customHeight="true">
       <c r="A61" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B61" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F61" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G61" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H61" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" ht="15.0" customHeight="true">
       <c r="A62" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B62" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G62" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H62" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="true">
       <c r="A63" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B63" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F63" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G63" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H63" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" ht="15.0" customHeight="true">
       <c r="A64" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B64" s="12" t="n">
         <v>10.0</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F64" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G64" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H64" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65" ht="15.0" customHeight="true">
       <c r="A65" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B65" s="12" t="n">
         <v>11.0</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F65" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G65" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H65" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="true">
       <c r="A66" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B66" s="12" t="n">
         <v>12.0</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F66" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G66" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H66" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67" ht="15.0" customHeight="true">
       <c r="A67" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B67" s="12" t="n">
         <v>13.0</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F67" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G67" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H67" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68" ht="15.0" customHeight="true">
       <c r="A68" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B68" s="12" t="n">
         <v>14.0</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F68" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G68" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H68" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="true">
       <c r="A69" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B69" s="12" t="n">
         <v>15.0</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F69" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G69" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H69" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" ht="15.0" customHeight="true">
       <c r="A70" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B70" s="12" t="n">
         <v>16.0</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F70" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G70" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H70" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71" ht="15.0" customHeight="true">
@@ -2390,11 +2388,9 @@
       <c r="A72" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B72" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B72" s="28"/>
       <c r="C72" s="29" t="s">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="D72" s="30"/>
       <c r="E72" s="31"/>
@@ -2404,13 +2400,11 @@
     </row>
     <row r="73" ht="15.0" customHeight="true">
       <c r="A73" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B73" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="B73" s="36"/>
       <c r="C73" s="37" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D73" s="38"/>
       <c r="E73" s="39"/>
@@ -2420,756 +2414,756 @@
     </row>
     <row r="74" ht="15.0" customHeight="true">
       <c r="A74" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B74" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C74" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D74" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E74" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F74" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G74" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H74" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75" ht="15.0" customHeight="true">
       <c r="A75" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B75" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C75" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D75" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E75" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F75" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G75" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H75" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76" ht="15.0" customHeight="true">
       <c r="A76" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B76" s="12" t="n">
         <v>1.0</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G76" s="17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H76" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" ht="15.0" customHeight="true">
       <c r="A77" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B77" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E77" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F77" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G77" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="F77" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G77" s="17" t="s">
-        <v>28</v>
-      </c>
       <c r="H77" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78" ht="15.0" customHeight="true">
       <c r="A78" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B78" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F78" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G78" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H78" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79" ht="15.0" customHeight="true">
       <c r="A79" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B79" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F79" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G79" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H79" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" ht="15.0" customHeight="true">
       <c r="A80" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B80" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F80" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G80" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H80" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81" ht="15.0" customHeight="true">
       <c r="A81" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B81" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F81" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G81" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H81" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82" ht="15.0" customHeight="true">
       <c r="A82" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B82" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F82" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G82" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H82" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" ht="15.0" customHeight="true">
       <c r="A83" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B83" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F83" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G83" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H83" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84" ht="15.0" customHeight="true">
       <c r="A84" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B84" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F84" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G84" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H84" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85" ht="15.0" customHeight="true">
       <c r="A85" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B85" s="12" t="n">
         <v>10.0</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F85" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G85" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H85" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86" ht="15.0" customHeight="true">
       <c r="A86" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B86" s="12" t="n">
         <v>11.0</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F86" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G86" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H86" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87" ht="15.0" customHeight="true">
       <c r="A87" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B87" s="12" t="n">
         <v>12.0</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F87" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G87" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H87" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88" ht="15.0" customHeight="true">
       <c r="A88" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B88" s="12" t="n">
         <v>13.0</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F88" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G88" s="17" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H88" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89" ht="15.0" customHeight="true">
       <c r="A89" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B89" s="12" t="n">
         <v>14.0</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D89" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E89" s="15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F89" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G89" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H89" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" ht="15.0" customHeight="true">
       <c r="A90" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B90" s="12" t="n">
         <v>15.0</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E90" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F90" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G90" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H90" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" ht="15.0" customHeight="true">
       <c r="A91" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B91" s="12" t="n">
         <v>16.0</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E91" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F91" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G91" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H91" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92" ht="15.0" customHeight="true">
       <c r="A92" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B92" s="12" t="n">
         <v>17.0</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F92" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G92" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H92" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93" ht="15.0" customHeight="true">
       <c r="A93" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B93" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C93" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D93" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E93" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F93" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G93" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H93" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94" ht="15.0" customHeight="true">
       <c r="A94" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B94" s="12" t="n">
         <v>1.0</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E94" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F94" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G94" s="17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H94" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95" ht="15.0" customHeight="true">
       <c r="A95" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B95" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E95" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F95" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G95" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H95" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96" ht="15.0" customHeight="true">
       <c r="A96" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B96" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C96" s="13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D96" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F96" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G96" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H96" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97" ht="15.0" customHeight="true">
       <c r="A97" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B97" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D97" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E97" s="15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F97" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G97" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H97" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98" ht="15.0" customHeight="true">
       <c r="A98" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B98" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D98" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F98" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G98" s="17" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H98" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99" ht="15.0" customHeight="true">
       <c r="A99" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B99" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E99" s="15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F99" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G99" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H99" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" ht="15.0" customHeight="true">
       <c r="A100" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B100" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E100" s="15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F100" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G100" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H100" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" ht="15.0" customHeight="true">
       <c r="A101" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B101" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E101" s="15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F101" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G101" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H101" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" ht="15.0" customHeight="true">
       <c r="A102" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B102" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F102" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G102" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H102" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103" ht="15.0" customHeight="true">
@@ -3186,11 +3180,9 @@
       <c r="A104" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B104" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B104" s="28"/>
       <c r="C104" s="29" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c r="D104" s="30"/>
       <c r="E104" s="31"/>
@@ -3200,13 +3192,11 @@
     </row>
     <row r="105" ht="15.0" customHeight="true">
       <c r="A105" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B105" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="B105" s="36"/>
       <c r="C105" s="37" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D105" s="38"/>
       <c r="E105" s="39"/>
@@ -3216,80 +3206,80 @@
     </row>
     <row r="106" ht="15.0" customHeight="true">
       <c r="A106" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B106" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C106" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D106" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E106" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F106" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G106" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H106" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107" ht="15.0" customHeight="true">
       <c r="A107" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B107" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C107" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D107" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E107" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F107" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G107" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H107" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="108" ht="15.0" customHeight="true">
       <c r="A108" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B108" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B108" s="12" t="n">
+        <v>1.0</v>
       </c>
       <c r="C108" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D108" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E108" s="15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F108" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G108" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H108" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="109" ht="15.0" customHeight="true">
@@ -3306,11 +3296,9 @@
       <c r="A110" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B110" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B110" s="28"/>
       <c r="C110" s="29" t="s">
-        <v>114</v>
+        <v>3</v>
       </c>
       <c r="D110" s="30"/>
       <c r="E110" s="31"/>
@@ -3320,13 +3308,11 @@
     </row>
     <row r="111" ht="15.0" customHeight="true">
       <c r="A111" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B111" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="B111" s="36"/>
       <c r="C111" s="37" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D111" s="38"/>
       <c r="E111" s="39"/>
@@ -3336,132 +3322,132 @@
     </row>
     <row r="112" ht="15.0" customHeight="true">
       <c r="A112" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B112" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C112" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D112" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E112" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F112" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G112" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H112" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113" ht="15.0" customHeight="true">
       <c r="A113" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B113" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C113" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D113" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E113" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F113" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G113" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H113" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="114" ht="15.0" customHeight="true">
       <c r="A114" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B114" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B114" s="12" t="n">
+        <v>1.0</v>
       </c>
       <c r="C114" s="13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D114" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E114" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F114" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G114" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H114" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="115" ht="15.0" customHeight="true">
       <c r="A115" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B115" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C115" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D115" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E115" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F115" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G115" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H115" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="116" ht="15.0" customHeight="true">
       <c r="A116" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C116" s="13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D116" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E116" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F116" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G116" s="17" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H116" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" ht="15.0" customHeight="true">
@@ -3478,11 +3464,9 @@
       <c r="A118" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B118" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B118" s="28"/>
       <c r="C118" s="29" t="s">
-        <v>119</v>
+        <v>3</v>
       </c>
       <c r="D118" s="30"/>
       <c r="E118" s="31"/>
@@ -3492,13 +3476,11 @@
     </row>
     <row r="119" ht="15.0" customHeight="true">
       <c r="A119" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B119" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="B119" s="36"/>
       <c r="C119" s="37" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D119" s="38"/>
       <c r="E119" s="39"/>
@@ -3508,522 +3490,522 @@
     </row>
     <row r="120" ht="15.0" customHeight="true">
       <c r="A120" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B120" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C120" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D120" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E120" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F120" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G120" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H120" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="121" ht="15.0" customHeight="true">
       <c r="A121" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B121" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C121" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D121" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E121" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F121" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G121" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H121" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="122" ht="15.0" customHeight="true">
       <c r="A122" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B122" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B122" s="12" t="n">
+        <v>1.0</v>
       </c>
       <c r="C122" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D122" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E122" s="15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F122" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G122" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H122" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" ht="15.0" customHeight="true">
       <c r="A123" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B123" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C123" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D123" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E123" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F123" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G123" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H123" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="124" ht="15.0" customHeight="true">
       <c r="A124" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B124" s="12" t="n">
         <v>1.0</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D124" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E124" s="15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F124" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G124" s="17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H124" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125" ht="15.0" customHeight="true">
       <c r="A125" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B125" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C125" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D125" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E125" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F125" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G125" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H125" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="126" ht="15.0" customHeight="true">
       <c r="A126" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B126" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C126" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D126" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E126" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F126" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G126" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H126" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="127" ht="15.0" customHeight="true">
       <c r="A127" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B127" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C127" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D127" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E127" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F127" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G127" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="F127" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G127" s="17" t="s">
-        <v>28</v>
-      </c>
       <c r="H127" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128" ht="15.0" customHeight="true">
       <c r="A128" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B128" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D128" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E128" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F128" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G128" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H128" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129" ht="15.0" customHeight="true">
       <c r="A129" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B129" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C129" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D129" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E129" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F129" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G129" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H129" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="130" ht="15.0" customHeight="true">
       <c r="A130" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B130" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C130" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D130" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E130" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F130" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G130" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H130" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="131" ht="15.0" customHeight="true">
       <c r="A131" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B131" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C131" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D131" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E131" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F131" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G131" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H131" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="132" ht="15.0" customHeight="true">
       <c r="A132" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B132" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C132" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D132" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E132" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F132" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G132" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H132" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="133" ht="15.0" customHeight="true">
       <c r="A133" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B133" s="12" t="n">
         <v>10.0</v>
       </c>
       <c r="C133" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D133" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E133" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F133" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G133" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H133" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="134" ht="15.0" customHeight="true">
       <c r="A134" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B134" s="12" t="n">
         <v>11.0</v>
       </c>
       <c r="C134" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D134" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E134" s="15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F134" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G134" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H134" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135" ht="15.0" customHeight="true">
       <c r="A135" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B135" s="12" t="n">
         <v>12.0</v>
       </c>
       <c r="C135" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D135" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E135" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F135" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G135" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H135" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136" ht="15.0" customHeight="true">
       <c r="A136" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B136" s="12" t="n">
         <v>13.0</v>
       </c>
       <c r="C136" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D136" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E136" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F136" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G136" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H136" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="137" ht="15.0" customHeight="true">
       <c r="A137" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B137" s="12" t="n">
         <v>14.0</v>
       </c>
       <c r="C137" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D137" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E137" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F137" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G137" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H137" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="138" ht="15.0" customHeight="true">
       <c r="A138" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B138" s="12" t="n">
         <v>15.0</v>
       </c>
       <c r="C138" s="13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D138" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E138" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F138" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G138" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H138" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="139" ht="15.0" customHeight="true">
       <c r="A139" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B139" s="12" t="n">
         <v>16.0</v>
       </c>
       <c r="C139" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D139" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E139" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F139" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G139" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H139" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="140" ht="15.0" customHeight="true">
@@ -4040,11 +4022,9 @@
       <c r="A141" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B141" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B141" s="28"/>
       <c r="C141" s="29" t="s">
-        <v>121</v>
+        <v>3</v>
       </c>
       <c r="D141" s="30"/>
       <c r="E141" s="31"/>
@@ -4054,13 +4034,11 @@
     </row>
     <row r="142" ht="15.0" customHeight="true">
       <c r="A142" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B142" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="B142" s="36"/>
       <c r="C142" s="37" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D142" s="38"/>
       <c r="E142" s="39"/>
@@ -4070,522 +4048,522 @@
     </row>
     <row r="143" ht="15.0" customHeight="true">
       <c r="A143" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B143" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C143" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D143" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E143" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F143" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G143" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H143" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="144" ht="15.0" customHeight="true">
       <c r="A144" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B144" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C144" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D144" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E144" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F144" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G144" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H144" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="145" ht="15.0" customHeight="true">
       <c r="A145" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B145" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B145" s="12" t="n">
+        <v>1.0</v>
       </c>
       <c r="C145" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D145" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E145" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F145" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G145" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H145" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="146" ht="15.0" customHeight="true">
       <c r="A146" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B146" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C146" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D146" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E146" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F146" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G146" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H146" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="147" ht="15.0" customHeight="true">
       <c r="A147" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B147" s="12" t="n">
         <v>1.0</v>
       </c>
       <c r="C147" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D147" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E147" s="15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F147" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G147" s="17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H147" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="148" ht="15.0" customHeight="true">
       <c r="A148" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B148" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C148" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D148" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E148" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F148" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G148" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H148" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="149" ht="15.0" customHeight="true">
       <c r="A149" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B149" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C149" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D149" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E149" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F149" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G149" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H149" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="150" ht="15.0" customHeight="true">
       <c r="A150" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B150" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C150" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D150" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E150" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F150" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G150" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="F150" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G150" s="17" t="s">
-        <v>28</v>
-      </c>
       <c r="H150" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="151" ht="15.0" customHeight="true">
       <c r="A151" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B151" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C151" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D151" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E151" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F151" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G151" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H151" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="152" ht="15.0" customHeight="true">
       <c r="A152" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B152" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C152" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D152" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E152" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F152" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G152" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H152" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="153" ht="15.0" customHeight="true">
       <c r="A153" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B153" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C153" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D153" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E153" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F153" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G153" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H153" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="154" ht="15.0" customHeight="true">
       <c r="A154" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B154" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C154" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D154" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E154" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F154" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G154" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H154" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="155" ht="15.0" customHeight="true">
       <c r="A155" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B155" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C155" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D155" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E155" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F155" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G155" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H155" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="156" ht="15.0" customHeight="true">
       <c r="A156" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B156" s="12" t="n">
         <v>10.0</v>
       </c>
       <c r="C156" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D156" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E156" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F156" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G156" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H156" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="157" ht="15.0" customHeight="true">
       <c r="A157" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B157" s="12" t="n">
         <v>11.0</v>
       </c>
       <c r="C157" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D157" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E157" s="15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F157" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G157" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H157" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="158" ht="15.0" customHeight="true">
       <c r="A158" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B158" s="12" t="n">
         <v>12.0</v>
       </c>
       <c r="C158" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D158" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E158" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F158" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G158" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H158" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="159" ht="15.0" customHeight="true">
       <c r="A159" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B159" s="12" t="n">
         <v>13.0</v>
       </c>
       <c r="C159" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D159" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E159" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F159" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G159" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H159" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="160" ht="15.0" customHeight="true">
       <c r="A160" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B160" s="12" t="n">
         <v>14.0</v>
       </c>
       <c r="C160" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D160" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E160" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F160" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G160" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H160" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="161" ht="15.0" customHeight="true">
       <c r="A161" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B161" s="12" t="n">
         <v>15.0</v>
       </c>
       <c r="C161" s="13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D161" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E161" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F161" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G161" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H161" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="162" ht="15.0" customHeight="true">
       <c r="A162" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B162" s="12" t="n">
         <v>16.0</v>
       </c>
       <c r="C162" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D162" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E162" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F162" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G162" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H162" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="163" ht="15.0" customHeight="true">
@@ -4602,11 +4580,9 @@
       <c r="A164" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B164" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B164" s="28"/>
       <c r="C164" s="29" t="s">
-        <v>125</v>
+        <v>3</v>
       </c>
       <c r="D164" s="30"/>
       <c r="E164" s="31"/>
@@ -4616,13 +4592,11 @@
     </row>
     <row r="165" ht="15.0" customHeight="true">
       <c r="A165" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B165" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="B165" s="36"/>
       <c r="C165" s="37" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D165" s="38"/>
       <c r="E165" s="39"/>
@@ -4632,132 +4606,132 @@
     </row>
     <row r="166" ht="15.0" customHeight="true">
       <c r="A166" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B166" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C166" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D166" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E166" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F166" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G166" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H166" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="167" ht="15.0" customHeight="true">
       <c r="A167" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B167" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C167" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D167" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E167" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F167" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G167" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H167" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="168" ht="15.0" customHeight="true">
       <c r="A168" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B168" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B168" s="12" t="n">
+        <v>1.0</v>
       </c>
       <c r="C168" s="13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D168" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E168" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F168" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G168" s="17" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H168" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="169" ht="15.0" customHeight="true">
       <c r="A169" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B169" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C169" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D169" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E169" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F169" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G169" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H169" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="170" ht="15.0" customHeight="true">
       <c r="A170" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B170" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C170" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D170" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E170" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F170" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G170" s="17" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H170" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="171" ht="15.0" customHeight="true">
@@ -4772,13 +4746,13 @@
     </row>
     <row r="172" ht="15.0" customHeight="true">
       <c r="A172" s="67" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B172" s="68" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C172" s="69" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D172" s="70"/>
       <c r="E172" s="71"/>
@@ -4787,111 +4761,145 @@
       <c r="H172" s="74"/>
     </row>
     <row r="173">
-      <c r="A173" s="5" t="s">
-        <v>133</v>
+      <c r="A173" s="10" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="5" t="s">
-        <v>134</v>
+      <c r="A174" s="10" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="5" t="s">
-        <v>135</v>
+      <c r="A175" s="10" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="5" t="s">
-        <v>136</v>
+      <c r="A176" s="10" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="5" t="s">
-        <v>12</v>
+      <c r="A177" s="10" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="5" t="s">
-        <v>137</v>
+      <c r="A178" s="10" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="5" t="s">
-        <v>138</v>
+      <c r="A179" s="10" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="5" t="s">
-        <v>139</v>
+      <c r="A180" s="10" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="5" t="s">
-        <v>140</v>
+      <c r="A181" s="10" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="5" t="s">
-        <v>141</v>
+      <c r="A182" s="10" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="5" t="s">
-        <v>142</v>
+      <c r="A183" s="10" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="5" t="s">
-        <v>143</v>
+      <c r="A184" s="10" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="5" t="s">
-        <v>144</v>
+      <c r="A185" s="10" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="5" t="s">
-        <v>145</v>
+      <c r="A186" s="10" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="5" t="s">
-        <v>12</v>
+      <c r="A187" s="10" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="5" t="s">
-        <v>146</v>
+      <c r="A188" s="10" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="s">
-        <v>147</v>
+      <c r="A189" s="10" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="5" t="s">
-        <v>148</v>
+      <c r="A190" s="10" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="5" t="s">
-        <v>149</v>
+      <c r="A191" s="10" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="5" t="s">
-        <v>12</v>
+      <c r="A192" s="10" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="5" t="s">
-        <v>150</v>
+      <c r="A193" s="10" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:H72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:H73"/>
+    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="C104:H104"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="C105:H105"/>
+    <mergeCell ref="A110:B110"/>
+    <mergeCell ref="C110:H110"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="C111:H111"/>
+    <mergeCell ref="A118:B118"/>
+    <mergeCell ref="C118:H118"/>
+    <mergeCell ref="A119:B119"/>
+    <mergeCell ref="C119:H119"/>
+    <mergeCell ref="A141:B141"/>
+    <mergeCell ref="C141:H141"/>
+    <mergeCell ref="A142:B142"/>
+    <mergeCell ref="C142:H142"/>
+    <mergeCell ref="A164:B164"/>
+    <mergeCell ref="C164:H164"/>
+    <mergeCell ref="A165:B165"/>
+    <mergeCell ref="C165:H165"/>
+  </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/output/BookRepository.xlsx
+++ b/output/BookRepository.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="208">
   <si>
     <t xml:space="preserve">Repository</t>
   </si>
@@ -247,15 +247,12 @@
     <t>書籍エンティティ。</t>
   </si>
   <si>
-    <t>BOOK</t>
+    <t>-</t>
   </si>
   <si>
     <t>Book</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t xml:space="preserve">  書籍ID</t>
   </si>
   <si>
@@ -373,7 +370,7 @@
     <t xml:space="preserve">  監査情報</t>
   </si>
   <si>
-    <t xml:space="preserve">  AUDIT_INFO</t>
+    <t xml:space="preserve">  -</t>
   </si>
   <si>
     <t xml:space="preserve">  auditInfo</t>
@@ -439,9 +436,6 @@
     <t>検索条件</t>
   </si>
   <si>
-    <t>CONDITION</t>
-  </si>
-  <si>
     <t>condition</t>
   </si>
   <si>
@@ -529,9 +523,6 @@
     <t>ページング要求</t>
   </si>
   <si>
-    <t>PAGE_REQUEST</t>
-  </si>
-  <si>
     <t>pageRequest</t>
   </si>
   <si>
@@ -550,9 +541,6 @@
     <t>ページング結果を表す共通DTO。</t>
   </si>
   <si>
-    <t>PAGE_RESULT</t>
-  </si>
-  <si>
     <t>PageResult</t>
   </si>
   <si>
@@ -562,9 +550,6 @@
     <t xml:space="preserve">  取得結果</t>
   </si>
   <si>
-    <t xml:space="preserve">  CONTENT</t>
-  </si>
-  <si>
     <t xml:space="preserve">  content</t>
   </si>
   <si>
@@ -590,9 +575,6 @@
   </si>
   <si>
     <t xml:space="preserve">  ページング要求</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  PAGE_REQUEST</t>
   </si>
   <si>
     <t xml:space="preserve">  pageRequest</t>
@@ -700,9 +682,6 @@
     <t>書籍ID配列</t>
   </si>
   <si>
-    <t>IDS</t>
-  </si>
-  <si>
     <t>ids</t>
   </si>
   <si>
@@ -710,9 +689,6 @@
   </si>
   <si>
     <t>Book[]</t>
-  </si>
-  <si>
-    <t>BOOK[]</t>
   </si>
   <si>
     <t>XML</t>
@@ -1664,7 +1640,7 @@
         <v>42</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>42</v>
@@ -1681,13 +1657,13 @@
         <v>2.0</v>
       </c>
       <c r="C18" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="E18" s="19" t="s">
         <v>45</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>46</v>
       </c>
       <c r="F18" s="20" t="s">
         <v>37</v>
@@ -1707,19 +1683,19 @@
         <v>3.0</v>
       </c>
       <c r="C19" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="19" t="s">
+      <c r="F19" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="G19" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H19" s="22" t="s">
         <v>17</v>
@@ -1733,19 +1709,19 @@
         <v>4.0</v>
       </c>
       <c r="C20" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="E20" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E20" s="19" t="s">
-        <v>53</v>
-      </c>
       <c r="F20" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H20" s="22" t="s">
         <v>17</v>
@@ -1759,19 +1735,19 @@
         <v>5.0</v>
       </c>
       <c r="C21" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="E21" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="E21" s="19" t="s">
-        <v>56</v>
-      </c>
       <c r="F21" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G21" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H21" s="22" t="s">
         <v>17</v>
@@ -1785,19 +1761,19 @@
         <v>6.0</v>
       </c>
       <c r="C22" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="E22" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="E22" s="19" t="s">
-        <v>59</v>
-      </c>
       <c r="F22" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G22" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H22" s="22" t="s">
         <v>17</v>
@@ -1811,19 +1787,19 @@
         <v>7.0</v>
       </c>
       <c r="C23" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="E23" s="19" t="s">
         <v>61</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>62</v>
       </c>
       <c r="F23" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G23" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H23" s="22" t="s">
         <v>17</v>
@@ -1837,19 +1813,19 @@
         <v>8.0</v>
       </c>
       <c r="C24" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="E24" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="F24" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="G24" s="21" t="s">
         <v>67</v>
-      </c>
-      <c r="G24" s="21" t="s">
-        <v>68</v>
       </c>
       <c r="H24" s="22" t="s">
         <v>17</v>
@@ -1863,19 +1839,19 @@
         <v>9.0</v>
       </c>
       <c r="C25" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="E25" s="19" t="s">
         <v>70</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>71</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H25" s="22" t="s">
         <v>17</v>
@@ -1889,19 +1865,19 @@
         <v>10.0</v>
       </c>
       <c r="C26" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="E26" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="F26" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="F26" s="20" t="s">
+      <c r="G26" s="21" t="s">
         <v>76</v>
-      </c>
-      <c r="G26" s="21" t="s">
-        <v>77</v>
       </c>
       <c r="H26" s="22" t="s">
         <v>17</v>
@@ -1915,19 +1891,19 @@
         <v>11.0</v>
       </c>
       <c r="C27" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="E27" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E27" s="19" t="s">
+      <c r="F27" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27" s="21" t="s">
         <v>80</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G27" s="21" t="s">
-        <v>81</v>
       </c>
       <c r="H27" s="22" t="s">
         <v>17</v>
@@ -1941,19 +1917,19 @@
         <v>12.0</v>
       </c>
       <c r="C28" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="E28" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="F28" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G28" s="21" t="s">
         <v>84</v>
-      </c>
-      <c r="F28" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G28" s="21" t="s">
-        <v>85</v>
       </c>
       <c r="H28" s="22" t="s">
         <v>17</v>
@@ -1967,19 +1943,19 @@
         <v>13.0</v>
       </c>
       <c r="C29" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="E29" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E29" s="19" t="s">
-        <v>88</v>
-      </c>
       <c r="F29" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G29" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G29" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H29" s="22" t="s">
         <v>17</v>
@@ -1993,19 +1969,19 @@
         <v>14.0</v>
       </c>
       <c r="C30" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="E30" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E30" s="19" t="s">
-        <v>91</v>
-      </c>
       <c r="F30" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G30" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H30" s="22" t="s">
         <v>17</v>
@@ -2019,19 +1995,19 @@
         <v>15.0</v>
       </c>
       <c r="C31" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="E31" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="E31" s="19" t="s">
-        <v>94</v>
-      </c>
       <c r="F31" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G31" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G31" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H31" s="22" t="s">
         <v>17</v>
@@ -2045,19 +2021,19 @@
         <v>16.0</v>
       </c>
       <c r="C32" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="E32" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="E32" s="19" t="s">
-        <v>97</v>
-      </c>
       <c r="F32" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H32" s="22" t="s">
         <v>17</v>
@@ -2089,11 +2065,11 @@
     </row>
     <row r="35" ht="15.0" customHeight="true">
       <c r="A35" s="39" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B35" s="40"/>
       <c r="C35" s="41" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D35" s="42"/>
       <c r="E35" s="43"/>
@@ -2161,16 +2137,16 @@
         <v>1.0</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D38" s="18" t="s">
         <v>41</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G38" s="21" t="s">
         <v>42</v>
@@ -2187,13 +2163,13 @@
         <v>2.0</v>
       </c>
       <c r="C39" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="E39" s="19" t="s">
         <v>45</v>
-      </c>
-      <c r="E39" s="19" t="s">
-        <v>46</v>
       </c>
       <c r="F39" s="20" t="s">
         <v>37</v>
@@ -2213,19 +2189,19 @@
         <v>3.0</v>
       </c>
       <c r="C40" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E40" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D40" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E40" s="19" t="s">
+      <c r="F40" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F40" s="20" t="s">
+      <c r="G40" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G40" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H40" s="22" t="s">
         <v>17</v>
@@ -2239,19 +2215,19 @@
         <v>4.0</v>
       </c>
       <c r="C41" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="E41" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E41" s="19" t="s">
-        <v>53</v>
-      </c>
       <c r="F41" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G41" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G41" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H41" s="22" t="s">
         <v>17</v>
@@ -2265,19 +2241,19 @@
         <v>5.0</v>
       </c>
       <c r="C42" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="E42" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="E42" s="19" t="s">
-        <v>56</v>
-      </c>
       <c r="F42" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G42" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G42" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H42" s="22" t="s">
         <v>17</v>
@@ -2291,19 +2267,19 @@
         <v>6.0</v>
       </c>
       <c r="C43" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="E43" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="E43" s="19" t="s">
-        <v>59</v>
-      </c>
       <c r="F43" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G43" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G43" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H43" s="22" t="s">
         <v>17</v>
@@ -2317,19 +2293,19 @@
         <v>7.0</v>
       </c>
       <c r="C44" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="E44" s="19" t="s">
         <v>61</v>
-      </c>
-      <c r="E44" s="19" t="s">
-        <v>62</v>
       </c>
       <c r="F44" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G44" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H44" s="22" t="s">
         <v>17</v>
@@ -2343,19 +2319,19 @@
         <v>8.0</v>
       </c>
       <c r="C45" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D45" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="E45" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="E45" s="19" t="s">
+      <c r="F45" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="F45" s="20" t="s">
+      <c r="G45" s="21" t="s">
         <v>67</v>
-      </c>
-      <c r="G45" s="21" t="s">
-        <v>68</v>
       </c>
       <c r="H45" s="22" t="s">
         <v>17</v>
@@ -2369,19 +2345,19 @@
         <v>9.0</v>
       </c>
       <c r="C46" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D46" s="18" t="s">
+      <c r="E46" s="19" t="s">
         <v>70</v>
-      </c>
-      <c r="E46" s="19" t="s">
-        <v>71</v>
       </c>
       <c r="F46" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G46" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H46" s="22" t="s">
         <v>17</v>
@@ -2395,19 +2371,19 @@
         <v>10.0</v>
       </c>
       <c r="C47" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D47" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="E47" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="F47" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="F47" s="20" t="s">
+      <c r="G47" s="21" t="s">
         <v>76</v>
-      </c>
-      <c r="G47" s="21" t="s">
-        <v>77</v>
       </c>
       <c r="H47" s="22" t="s">
         <v>17</v>
@@ -2421,19 +2397,19 @@
         <v>11.0</v>
       </c>
       <c r="C48" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D48" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D48" s="18" t="s">
+      <c r="E48" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E48" s="19" t="s">
+      <c r="F48" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="G48" s="21" t="s">
         <v>80</v>
-      </c>
-      <c r="F48" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G48" s="21" t="s">
-        <v>81</v>
       </c>
       <c r="H48" s="22" t="s">
         <v>17</v>
@@ -2447,19 +2423,19 @@
         <v>12.0</v>
       </c>
       <c r="C49" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D49" s="18" t="s">
+      <c r="E49" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="E49" s="19" t="s">
+      <c r="F49" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G49" s="21" t="s">
         <v>84</v>
-      </c>
-      <c r="F49" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G49" s="21" t="s">
-        <v>85</v>
       </c>
       <c r="H49" s="22" t="s">
         <v>17</v>
@@ -2473,19 +2449,19 @@
         <v>13.0</v>
       </c>
       <c r="C50" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D50" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="E50" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E50" s="19" t="s">
-        <v>88</v>
-      </c>
       <c r="F50" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G50" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G50" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H50" s="22" t="s">
         <v>17</v>
@@ -2499,19 +2475,19 @@
         <v>14.0</v>
       </c>
       <c r="C51" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D51" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D51" s="18" t="s">
+      <c r="E51" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E51" s="19" t="s">
-        <v>91</v>
-      </c>
       <c r="F51" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G51" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H51" s="22" t="s">
         <v>17</v>
@@ -2525,19 +2501,19 @@
         <v>15.0</v>
       </c>
       <c r="C52" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D52" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D52" s="18" t="s">
+      <c r="E52" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="E52" s="19" t="s">
-        <v>94</v>
-      </c>
       <c r="F52" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G52" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G52" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H52" s="22" t="s">
         <v>17</v>
@@ -2551,19 +2527,19 @@
         <v>16.0</v>
       </c>
       <c r="C53" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D53" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="D53" s="18" t="s">
+      <c r="E53" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="E53" s="19" t="s">
-        <v>97</v>
-      </c>
       <c r="F53" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G53" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H53" s="22" t="s">
         <v>17</v>
@@ -2612,7 +2588,7 @@
         <v>42</v>
       </c>
       <c r="F55" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G55" s="21" t="s">
         <v>42</v>
@@ -2629,13 +2605,13 @@
         <v>2.0</v>
       </c>
       <c r="C56" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D56" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D56" s="18" t="s">
+      <c r="E56" s="19" t="s">
         <v>45</v>
-      </c>
-      <c r="E56" s="19" t="s">
-        <v>46</v>
       </c>
       <c r="F56" s="20" t="s">
         <v>37</v>
@@ -2655,19 +2631,19 @@
         <v>3.0</v>
       </c>
       <c r="C57" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D57" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E57" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D57" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E57" s="19" t="s">
+      <c r="F57" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F57" s="20" t="s">
+      <c r="G57" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G57" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H57" s="22" t="s">
         <v>17</v>
@@ -2681,19 +2657,19 @@
         <v>4.0</v>
       </c>
       <c r="C58" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D58" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="18" t="s">
+      <c r="E58" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E58" s="19" t="s">
-        <v>53</v>
-      </c>
       <c r="F58" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G58" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G58" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H58" s="22" t="s">
         <v>17</v>
@@ -2707,19 +2683,19 @@
         <v>5.0</v>
       </c>
       <c r="C59" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D59" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D59" s="18" t="s">
+      <c r="E59" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="E59" s="19" t="s">
-        <v>56</v>
-      </c>
       <c r="F59" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G59" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G59" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H59" s="22" t="s">
         <v>17</v>
@@ -2733,19 +2709,19 @@
         <v>6.0</v>
       </c>
       <c r="C60" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D60" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D60" s="18" t="s">
+      <c r="E60" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="E60" s="19" t="s">
-        <v>59</v>
-      </c>
       <c r="F60" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G60" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G60" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H60" s="22" t="s">
         <v>17</v>
@@ -2759,19 +2735,19 @@
         <v>7.0</v>
       </c>
       <c r="C61" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D61" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D61" s="18" t="s">
+      <c r="E61" s="19" t="s">
         <v>61</v>
-      </c>
-      <c r="E61" s="19" t="s">
-        <v>62</v>
       </c>
       <c r="F61" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G61" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H61" s="22" t="s">
         <v>17</v>
@@ -2785,19 +2761,19 @@
         <v>8.0</v>
       </c>
       <c r="C62" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D62" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D62" s="18" t="s">
+      <c r="E62" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="E62" s="19" t="s">
+      <c r="F62" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="F62" s="20" t="s">
+      <c r="G62" s="21" t="s">
         <v>67</v>
-      </c>
-      <c r="G62" s="21" t="s">
-        <v>68</v>
       </c>
       <c r="H62" s="22" t="s">
         <v>17</v>
@@ -2811,19 +2787,19 @@
         <v>9.0</v>
       </c>
       <c r="C63" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D63" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D63" s="18" t="s">
+      <c r="E63" s="19" t="s">
         <v>70</v>
-      </c>
-      <c r="E63" s="19" t="s">
-        <v>71</v>
       </c>
       <c r="F63" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G63" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H63" s="22" t="s">
         <v>17</v>
@@ -2837,19 +2813,19 @@
         <v>10.0</v>
       </c>
       <c r="C64" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D64" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="D64" s="18" t="s">
+      <c r="E64" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="E64" s="19" t="s">
+      <c r="F64" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="F64" s="20" t="s">
+      <c r="G64" s="21" t="s">
         <v>76</v>
-      </c>
-      <c r="G64" s="21" t="s">
-        <v>77</v>
       </c>
       <c r="H64" s="22" t="s">
         <v>17</v>
@@ -2863,19 +2839,19 @@
         <v>11.0</v>
       </c>
       <c r="C65" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D65" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D65" s="18" t="s">
+      <c r="E65" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E65" s="19" t="s">
+      <c r="F65" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="G65" s="21" t="s">
         <v>80</v>
-      </c>
-      <c r="F65" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G65" s="21" t="s">
-        <v>81</v>
       </c>
       <c r="H65" s="22" t="s">
         <v>17</v>
@@ -2889,19 +2865,19 @@
         <v>12.0</v>
       </c>
       <c r="C66" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D66" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D66" s="18" t="s">
+      <c r="E66" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="E66" s="19" t="s">
+      <c r="F66" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G66" s="21" t="s">
         <v>84</v>
-      </c>
-      <c r="F66" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G66" s="21" t="s">
-        <v>85</v>
       </c>
       <c r="H66" s="22" t="s">
         <v>17</v>
@@ -2915,19 +2891,19 @@
         <v>13.0</v>
       </c>
       <c r="C67" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D67" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D67" s="18" t="s">
+      <c r="E67" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E67" s="19" t="s">
-        <v>88</v>
-      </c>
       <c r="F67" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G67" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G67" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H67" s="22" t="s">
         <v>17</v>
@@ -2941,19 +2917,19 @@
         <v>14.0</v>
       </c>
       <c r="C68" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D68" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D68" s="18" t="s">
+      <c r="E68" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E68" s="19" t="s">
-        <v>91</v>
-      </c>
       <c r="F68" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G68" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H68" s="22" t="s">
         <v>17</v>
@@ -2967,19 +2943,19 @@
         <v>15.0</v>
       </c>
       <c r="C69" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D69" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D69" s="18" t="s">
+      <c r="E69" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="E69" s="19" t="s">
-        <v>94</v>
-      </c>
       <c r="F69" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G69" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G69" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H69" s="22" t="s">
         <v>17</v>
@@ -2993,19 +2969,19 @@
         <v>16.0</v>
       </c>
       <c r="C70" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D70" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="D70" s="18" t="s">
+      <c r="E70" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="E70" s="19" t="s">
-        <v>97</v>
-      </c>
       <c r="F70" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G70" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H70" s="22" t="s">
         <v>17</v>
@@ -3037,11 +3013,11 @@
     </row>
     <row r="73" ht="15.0" customHeight="true">
       <c r="A73" s="39" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B73" s="40"/>
       <c r="C73" s="41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D73" s="42"/>
       <c r="E73" s="43"/>
@@ -3109,19 +3085,19 @@
         <v>1.0</v>
       </c>
       <c r="C76" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D76" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E76" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="D76" s="18" t="s">
+      <c r="F76" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G76" s="21" t="s">
         <v>105</v>
-      </c>
-      <c r="E76" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="F76" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G76" s="21" t="s">
-        <v>107</v>
       </c>
       <c r="H76" s="22" t="s">
         <v>17</v>
@@ -3135,19 +3111,19 @@
         <v>2.0</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D77" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E77" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E77" s="19" t="s">
-        <v>53</v>
-      </c>
       <c r="F77" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G77" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G77" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H77" s="22" t="s">
         <v>17</v>
@@ -3161,19 +3137,19 @@
         <v>3.0</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D78" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E78" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="E78" s="19" t="s">
-        <v>56</v>
-      </c>
       <c r="F78" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G78" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G78" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H78" s="22" t="s">
         <v>17</v>
@@ -3187,19 +3163,19 @@
         <v>4.0</v>
       </c>
       <c r="C79" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D79" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E79" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D79" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E79" s="19" t="s">
+      <c r="F79" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F79" s="20" t="s">
+      <c r="G79" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G79" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H79" s="22" t="s">
         <v>17</v>
@@ -3213,19 +3189,19 @@
         <v>5.0</v>
       </c>
       <c r="C80" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="D80" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E80" s="19" t="s">
         <v>110</v>
-      </c>
-      <c r="D80" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="E80" s="19" t="s">
-        <v>112</v>
       </c>
       <c r="F80" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G80" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H80" s="22" t="s">
         <v>17</v>
@@ -3239,19 +3215,19 @@
         <v>6.0</v>
       </c>
       <c r="C81" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D81" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E81" s="19" t="s">
         <v>113</v>
-      </c>
-      <c r="D81" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="E81" s="19" t="s">
-        <v>115</v>
       </c>
       <c r="F81" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G81" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H81" s="22" t="s">
         <v>17</v>
@@ -3265,19 +3241,19 @@
         <v>7.0</v>
       </c>
       <c r="C82" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="D82" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="E82" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="D82" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="E82" s="19" t="s">
-        <v>118</v>
-      </c>
       <c r="F82" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="G82" s="21" t="s">
         <v>67</v>
-      </c>
-      <c r="G82" s="21" t="s">
-        <v>68</v>
       </c>
       <c r="H82" s="22" t="s">
         <v>17</v>
@@ -3291,19 +3267,19 @@
         <v>8.0</v>
       </c>
       <c r="C83" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D83" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="E83" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="D83" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="E83" s="19" t="s">
-        <v>121</v>
-      </c>
       <c r="F83" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="G83" s="21" t="s">
         <v>67</v>
-      </c>
-      <c r="G83" s="21" t="s">
-        <v>68</v>
       </c>
       <c r="H83" s="22" t="s">
         <v>17</v>
@@ -3317,19 +3293,19 @@
         <v>9.0</v>
       </c>
       <c r="C84" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D84" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E84" s="19" t="s">
         <v>122</v>
-      </c>
-      <c r="D84" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="E84" s="19" t="s">
-        <v>124</v>
       </c>
       <c r="F84" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G84" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H84" s="22" t="s">
         <v>17</v>
@@ -3343,19 +3319,19 @@
         <v>10.0</v>
       </c>
       <c r="C85" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D85" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="E85" s="19" t="s">
         <v>125</v>
-      </c>
-      <c r="D85" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="E85" s="19" t="s">
-        <v>127</v>
       </c>
       <c r="F85" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G85" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H85" s="22" t="s">
         <v>17</v>
@@ -3369,19 +3345,19 @@
         <v>11.0</v>
       </c>
       <c r="C86" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="D86" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="E86" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="D86" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E86" s="19" t="s">
-        <v>130</v>
-      </c>
       <c r="F86" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G86" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G86" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H86" s="22" t="s">
         <v>17</v>
@@ -3395,19 +3371,19 @@
         <v>12.0</v>
       </c>
       <c r="C87" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="D87" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="E87" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="D87" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="E87" s="19" t="s">
-        <v>133</v>
-      </c>
       <c r="F87" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G87" s="21" t="s">
         <v>76</v>
-      </c>
-      <c r="G87" s="21" t="s">
-        <v>77</v>
       </c>
       <c r="H87" s="22" t="s">
         <v>17</v>
@@ -3421,19 +3397,19 @@
         <v>13.0</v>
       </c>
       <c r="C88" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="D88" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E88" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="F88" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G88" s="21" t="s">
         <v>134</v>
-      </c>
-      <c r="D88" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="E88" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="F88" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G88" s="21" t="s">
-        <v>137</v>
       </c>
       <c r="H88" s="22" t="s">
         <v>17</v>
@@ -3447,19 +3423,19 @@
         <v>14.0</v>
       </c>
       <c r="C89" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D89" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E89" s="19" t="s">
         <v>122</v>
-      </c>
-      <c r="D89" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="E89" s="19" t="s">
-        <v>124</v>
       </c>
       <c r="F89" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G89" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H89" s="22" t="s">
         <v>17</v>
@@ -3473,19 +3449,19 @@
         <v>15.0</v>
       </c>
       <c r="C90" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D90" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="E90" s="19" t="s">
         <v>125</v>
-      </c>
-      <c r="D90" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="E90" s="19" t="s">
-        <v>127</v>
       </c>
       <c r="F90" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G90" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H90" s="22" t="s">
         <v>17</v>
@@ -3499,19 +3475,19 @@
         <v>16.0</v>
       </c>
       <c r="C91" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="D91" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="E91" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="D91" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E91" s="19" t="s">
-        <v>130</v>
-      </c>
       <c r="F91" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G91" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G91" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H91" s="22" t="s">
         <v>17</v>
@@ -3525,19 +3501,19 @@
         <v>17.0</v>
       </c>
       <c r="C92" s="17" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D92" s="18" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E92" s="19" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F92" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G92" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G92" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H92" s="22" t="s">
         <v>17</v>
@@ -3577,19 +3553,19 @@
         <v>1.0</v>
       </c>
       <c r="C94" s="17" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D94" s="18" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="E94" s="19" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F94" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G94" s="21" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H94" s="22" t="s">
         <v>17</v>
@@ -3603,19 +3579,19 @@
         <v>2.0</v>
       </c>
       <c r="C95" s="17" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D95" s="18" t="s">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="E95" s="19" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F95" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G95" s="21" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="H95" s="22" t="s">
         <v>17</v>
@@ -3629,13 +3605,13 @@
         <v>3.0</v>
       </c>
       <c r="C96" s="17" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D96" s="18" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E96" s="19" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F96" s="20" t="s">
         <v>37</v>
@@ -3655,19 +3631,19 @@
         <v>4.0</v>
       </c>
       <c r="C97" s="17" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D97" s="18" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E97" s="19" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F97" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G97" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H97" s="22" t="s">
         <v>17</v>
@@ -3681,19 +3657,19 @@
         <v>5.0</v>
       </c>
       <c r="C98" s="17" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D98" s="18" t="s">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="E98" s="19" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F98" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G98" s="21" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H98" s="22" t="s">
         <v>17</v>
@@ -3707,19 +3683,19 @@
         <v>6.0</v>
       </c>
       <c r="C99" s="17" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D99" s="18" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E99" s="19" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F99" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G99" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H99" s="22" t="s">
         <v>17</v>
@@ -3733,19 +3709,19 @@
         <v>7.0</v>
       </c>
       <c r="C100" s="17" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D100" s="18" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E100" s="19" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="F100" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G100" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H100" s="22" t="s">
         <v>17</v>
@@ -3759,19 +3735,19 @@
         <v>8.0</v>
       </c>
       <c r="C101" s="17" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D101" s="18" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E101" s="19" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F101" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G101" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G101" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H101" s="22" t="s">
         <v>17</v>
@@ -3785,19 +3761,19 @@
         <v>9.0</v>
       </c>
       <c r="C102" s="17" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D102" s="18" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E102" s="19" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F102" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G102" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G102" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H102" s="22" t="s">
         <v>17</v>
@@ -3829,11 +3805,11 @@
     </row>
     <row r="105" ht="15.0" customHeight="true">
       <c r="A105" s="39" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B105" s="40"/>
       <c r="C105" s="41" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D105" s="42"/>
       <c r="E105" s="43"/>
@@ -3953,19 +3929,19 @@
         <v>1.0</v>
       </c>
       <c r="C110" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D110" s="18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E110" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F110" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G110" s="21" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="H110" s="22" t="s">
         <v>17</v>
@@ -3997,11 +3973,11 @@
     </row>
     <row r="113" ht="15.0" customHeight="true">
       <c r="A113" s="39" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B113" s="40"/>
       <c r="C113" s="41" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D113" s="42"/>
       <c r="E113" s="43"/>
@@ -4069,19 +4045,19 @@
         <v>1.0</v>
       </c>
       <c r="C116" s="17" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D116" s="18" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E116" s="19" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F116" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G116" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G116" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H116" s="22" t="s">
         <v>17</v>
@@ -4121,19 +4097,19 @@
         <v>1.0</v>
       </c>
       <c r="C118" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D118" s="18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E118" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F118" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G118" s="21" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="H118" s="22" t="s">
         <v>17</v>
@@ -4165,11 +4141,11 @@
     </row>
     <row r="121" ht="15.0" customHeight="true">
       <c r="A121" s="39" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B121" s="40"/>
       <c r="C121" s="41" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D121" s="42"/>
       <c r="E121" s="43"/>
@@ -4298,10 +4274,10 @@
         <v>42</v>
       </c>
       <c r="F126" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G126" s="21" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="H126" s="22" t="s">
         <v>17</v>
@@ -4315,13 +4291,13 @@
         <v>2.0</v>
       </c>
       <c r="C127" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D127" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D127" s="18" t="s">
+      <c r="E127" s="19" t="s">
         <v>45</v>
-      </c>
-      <c r="E127" s="19" t="s">
-        <v>46</v>
       </c>
       <c r="F127" s="20" t="s">
         <v>37</v>
@@ -4341,19 +4317,19 @@
         <v>3.0</v>
       </c>
       <c r="C128" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D128" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E128" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D128" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E128" s="19" t="s">
+      <c r="F128" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F128" s="20" t="s">
+      <c r="G128" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G128" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H128" s="22" t="s">
         <v>17</v>
@@ -4367,19 +4343,19 @@
         <v>4.0</v>
       </c>
       <c r="C129" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D129" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D129" s="18" t="s">
+      <c r="E129" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E129" s="19" t="s">
-        <v>53</v>
-      </c>
       <c r="F129" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G129" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G129" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H129" s="22" t="s">
         <v>17</v>
@@ -4393,19 +4369,19 @@
         <v>5.0</v>
       </c>
       <c r="C130" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D130" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D130" s="18" t="s">
+      <c r="E130" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="E130" s="19" t="s">
-        <v>56</v>
-      </c>
       <c r="F130" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G130" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G130" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H130" s="22" t="s">
         <v>17</v>
@@ -4419,19 +4395,19 @@
         <v>6.0</v>
       </c>
       <c r="C131" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D131" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D131" s="18" t="s">
+      <c r="E131" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="E131" s="19" t="s">
-        <v>59</v>
-      </c>
       <c r="F131" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G131" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G131" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H131" s="22" t="s">
         <v>17</v>
@@ -4445,19 +4421,19 @@
         <v>7.0</v>
       </c>
       <c r="C132" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D132" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D132" s="18" t="s">
+      <c r="E132" s="19" t="s">
         <v>61</v>
-      </c>
-      <c r="E132" s="19" t="s">
-        <v>62</v>
       </c>
       <c r="F132" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G132" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H132" s="22" t="s">
         <v>17</v>
@@ -4471,19 +4447,19 @@
         <v>8.0</v>
       </c>
       <c r="C133" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D133" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D133" s="18" t="s">
+      <c r="E133" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="E133" s="19" t="s">
+      <c r="F133" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="F133" s="20" t="s">
+      <c r="G133" s="21" t="s">
         <v>67</v>
-      </c>
-      <c r="G133" s="21" t="s">
-        <v>68</v>
       </c>
       <c r="H133" s="22" t="s">
         <v>17</v>
@@ -4497,19 +4473,19 @@
         <v>9.0</v>
       </c>
       <c r="C134" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D134" s="18" t="s">
+      <c r="E134" s="19" t="s">
         <v>70</v>
-      </c>
-      <c r="E134" s="19" t="s">
-        <v>71</v>
       </c>
       <c r="F134" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G134" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H134" s="22" t="s">
         <v>17</v>
@@ -4523,19 +4499,19 @@
         <v>10.0</v>
       </c>
       <c r="C135" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D135" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="D135" s="18" t="s">
+      <c r="E135" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="E135" s="19" t="s">
+      <c r="F135" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="F135" s="20" t="s">
+      <c r="G135" s="21" t="s">
         <v>76</v>
-      </c>
-      <c r="G135" s="21" t="s">
-        <v>77</v>
       </c>
       <c r="H135" s="22" t="s">
         <v>17</v>
@@ -4549,19 +4525,19 @@
         <v>11.0</v>
       </c>
       <c r="C136" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D136" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D136" s="18" t="s">
+      <c r="E136" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E136" s="19" t="s">
+      <c r="F136" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="G136" s="21" t="s">
         <v>80</v>
-      </c>
-      <c r="F136" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G136" s="21" t="s">
-        <v>81</v>
       </c>
       <c r="H136" s="22" t="s">
         <v>17</v>
@@ -4575,19 +4551,19 @@
         <v>12.0</v>
       </c>
       <c r="C137" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D137" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D137" s="18" t="s">
+      <c r="E137" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="E137" s="19" t="s">
+      <c r="F137" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G137" s="21" t="s">
         <v>84</v>
-      </c>
-      <c r="F137" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G137" s="21" t="s">
-        <v>85</v>
       </c>
       <c r="H137" s="22" t="s">
         <v>17</v>
@@ -4601,19 +4577,19 @@
         <v>13.0</v>
       </c>
       <c r="C138" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D138" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D138" s="18" t="s">
+      <c r="E138" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E138" s="19" t="s">
-        <v>88</v>
-      </c>
       <c r="F138" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G138" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G138" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H138" s="22" t="s">
         <v>17</v>
@@ -4627,19 +4603,19 @@
         <v>14.0</v>
       </c>
       <c r="C139" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D139" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D139" s="18" t="s">
+      <c r="E139" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E139" s="19" t="s">
-        <v>91</v>
-      </c>
       <c r="F139" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G139" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H139" s="22" t="s">
         <v>17</v>
@@ -4653,19 +4629,19 @@
         <v>15.0</v>
       </c>
       <c r="C140" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D140" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D140" s="18" t="s">
+      <c r="E140" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="E140" s="19" t="s">
-        <v>94</v>
-      </c>
       <c r="F140" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G140" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G140" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H140" s="22" t="s">
         <v>17</v>
@@ -4679,19 +4655,19 @@
         <v>16.0</v>
       </c>
       <c r="C141" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D141" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="D141" s="18" t="s">
+      <c r="E141" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="E141" s="19" t="s">
-        <v>97</v>
-      </c>
       <c r="F141" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G141" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H141" s="22" t="s">
         <v>17</v>
@@ -4723,11 +4699,11 @@
     </row>
     <row r="144" ht="15.0" customHeight="true">
       <c r="A144" s="39" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B144" s="40"/>
       <c r="C144" s="41" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D144" s="42"/>
       <c r="E144" s="43"/>
@@ -4795,19 +4771,19 @@
         <v>1.0</v>
       </c>
       <c r="C147" s="17" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D147" s="18" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E147" s="19" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F147" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="G147" s="21" t="s">
         <v>67</v>
-      </c>
-      <c r="G147" s="21" t="s">
-        <v>68</v>
       </c>
       <c r="H147" s="22" t="s">
         <v>17</v>
@@ -4856,10 +4832,10 @@
         <v>42</v>
       </c>
       <c r="F149" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G149" s="21" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H149" s="22" t="s">
         <v>17</v>
@@ -4873,13 +4849,13 @@
         <v>2.0</v>
       </c>
       <c r="C150" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D150" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D150" s="18" t="s">
+      <c r="E150" s="19" t="s">
         <v>45</v>
-      </c>
-      <c r="E150" s="19" t="s">
-        <v>46</v>
       </c>
       <c r="F150" s="20" t="s">
         <v>37</v>
@@ -4899,19 +4875,19 @@
         <v>3.0</v>
       </c>
       <c r="C151" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D151" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E151" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D151" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E151" s="19" t="s">
+      <c r="F151" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F151" s="20" t="s">
+      <c r="G151" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G151" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H151" s="22" t="s">
         <v>17</v>
@@ -4925,19 +4901,19 @@
         <v>4.0</v>
       </c>
       <c r="C152" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D152" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D152" s="18" t="s">
+      <c r="E152" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E152" s="19" t="s">
-        <v>53</v>
-      </c>
       <c r="F152" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G152" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G152" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H152" s="22" t="s">
         <v>17</v>
@@ -4951,19 +4927,19 @@
         <v>5.0</v>
       </c>
       <c r="C153" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D153" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D153" s="18" t="s">
+      <c r="E153" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="E153" s="19" t="s">
-        <v>56</v>
-      </c>
       <c r="F153" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G153" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G153" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H153" s="22" t="s">
         <v>17</v>
@@ -4977,19 +4953,19 @@
         <v>6.0</v>
       </c>
       <c r="C154" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D154" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D154" s="18" t="s">
+      <c r="E154" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="E154" s="19" t="s">
-        <v>59</v>
-      </c>
       <c r="F154" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G154" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G154" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H154" s="22" t="s">
         <v>17</v>
@@ -5003,19 +4979,19 @@
         <v>7.0</v>
       </c>
       <c r="C155" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D155" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D155" s="18" t="s">
+      <c r="E155" s="19" t="s">
         <v>61</v>
-      </c>
-      <c r="E155" s="19" t="s">
-        <v>62</v>
       </c>
       <c r="F155" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G155" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H155" s="22" t="s">
         <v>17</v>
@@ -5029,19 +5005,19 @@
         <v>8.0</v>
       </c>
       <c r="C156" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D156" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D156" s="18" t="s">
+      <c r="E156" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="E156" s="19" t="s">
+      <c r="F156" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="F156" s="20" t="s">
+      <c r="G156" s="21" t="s">
         <v>67</v>
-      </c>
-      <c r="G156" s="21" t="s">
-        <v>68</v>
       </c>
       <c r="H156" s="22" t="s">
         <v>17</v>
@@ -5055,19 +5031,19 @@
         <v>9.0</v>
       </c>
       <c r="C157" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D157" s="18" t="s">
+      <c r="E157" s="19" t="s">
         <v>70</v>
-      </c>
-      <c r="E157" s="19" t="s">
-        <v>71</v>
       </c>
       <c r="F157" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G157" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H157" s="22" t="s">
         <v>17</v>
@@ -5081,19 +5057,19 @@
         <v>10.0</v>
       </c>
       <c r="C158" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D158" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="D158" s="18" t="s">
+      <c r="E158" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="E158" s="19" t="s">
+      <c r="F158" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="F158" s="20" t="s">
+      <c r="G158" s="21" t="s">
         <v>76</v>
-      </c>
-      <c r="G158" s="21" t="s">
-        <v>77</v>
       </c>
       <c r="H158" s="22" t="s">
         <v>17</v>
@@ -5107,19 +5083,19 @@
         <v>11.0</v>
       </c>
       <c r="C159" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D159" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D159" s="18" t="s">
+      <c r="E159" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E159" s="19" t="s">
+      <c r="F159" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="G159" s="21" t="s">
         <v>80</v>
-      </c>
-      <c r="F159" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G159" s="21" t="s">
-        <v>81</v>
       </c>
       <c r="H159" s="22" t="s">
         <v>17</v>
@@ -5133,19 +5109,19 @@
         <v>12.0</v>
       </c>
       <c r="C160" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D160" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D160" s="18" t="s">
+      <c r="E160" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="E160" s="19" t="s">
+      <c r="F160" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G160" s="21" t="s">
         <v>84</v>
-      </c>
-      <c r="F160" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G160" s="21" t="s">
-        <v>85</v>
       </c>
       <c r="H160" s="22" t="s">
         <v>17</v>
@@ -5159,19 +5135,19 @@
         <v>13.0</v>
       </c>
       <c r="C161" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D161" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D161" s="18" t="s">
+      <c r="E161" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E161" s="19" t="s">
-        <v>88</v>
-      </c>
       <c r="F161" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G161" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G161" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H161" s="22" t="s">
         <v>17</v>
@@ -5185,19 +5161,19 @@
         <v>14.0</v>
       </c>
       <c r="C162" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D162" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D162" s="18" t="s">
+      <c r="E162" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E162" s="19" t="s">
-        <v>91</v>
-      </c>
       <c r="F162" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G162" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H162" s="22" t="s">
         <v>17</v>
@@ -5211,19 +5187,19 @@
         <v>15.0</v>
       </c>
       <c r="C163" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D163" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D163" s="18" t="s">
+      <c r="E163" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="E163" s="19" t="s">
-        <v>94</v>
-      </c>
       <c r="F163" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G163" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G163" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H163" s="22" t="s">
         <v>17</v>
@@ -5237,19 +5213,19 @@
         <v>16.0</v>
       </c>
       <c r="C164" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D164" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="D164" s="18" t="s">
+      <c r="E164" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="E164" s="19" t="s">
-        <v>97</v>
-      </c>
       <c r="F164" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G164" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H164" s="22" t="s">
         <v>17</v>
@@ -5281,11 +5257,11 @@
     </row>
     <row r="167" ht="15.0" customHeight="true">
       <c r="A167" s="39" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B167" s="40"/>
       <c r="C167" s="41" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D167" s="42"/>
       <c r="E167" s="43"/>
@@ -5353,19 +5329,19 @@
         <v>1.0</v>
       </c>
       <c r="C170" s="17" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D170" s="18" t="s">
-        <v>191</v>
+        <v>41</v>
       </c>
       <c r="E170" s="19" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="F170" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G170" s="21" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="H170" s="22" t="s">
         <v>17</v>
@@ -5405,19 +5381,19 @@
         <v>1.0</v>
       </c>
       <c r="C172" s="17" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D172" s="18" t="s">
-        <v>195</v>
+        <v>41</v>
       </c>
       <c r="E172" s="19" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="F172" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G172" s="21" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="H172" s="22" t="s">
         <v>17</v>
@@ -5435,13 +5411,13 @@
     </row>
     <row r="174" ht="15.0" customHeight="true">
       <c r="A174" s="71" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B174" s="72" t="s">
         <v>17</v>
       </c>
       <c r="C174" s="73" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D174" s="74"/>
       <c r="E174" s="75"/>
@@ -5451,22 +5427,22 @@
     </row>
     <row r="175">
       <c r="A175" s="14" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="14" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="14" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="14" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="179">
@@ -5476,47 +5452,47 @@
     </row>
     <row r="180">
       <c r="A180" s="14" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="14" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="14" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="14" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="14" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="14" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="14" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="14" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="14" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
     <row r="189">
@@ -5526,22 +5502,22 @@
     </row>
     <row r="190">
       <c r="A190" s="14" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="14" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="14" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="14" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="194">
@@ -5551,7 +5527,7 @@
     </row>
     <row r="195">
       <c r="A195" s="14" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
